--- a/finetrace_overhead_stat.xlsx
+++ b/finetrace_overhead_stat.xlsx
@@ -1,16 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\FineTrace\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B2C6F1C-49DE-4933-94CF-BE97552F8D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results_cpu" sheetId="1" r:id="rId1"/>
     <sheet name="Results_gpu" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -44,26 +55,26 @@
     <t>cl_gemm</t>
   </si>
   <si>
-    <t>bench_b+tree</t>
+    <t>ze_gemm</t>
   </si>
   <si>
-    <t>bench_bfs</t>
+    <t>b+tree</t>
   </si>
   <si>
-    <t>bench_gaussian</t>
+    <t>bfs</t>
   </si>
   <si>
-    <t>bench_nw</t>
+    <t>gaussian</t>
   </si>
   <si>
-    <t>ze_gemm</t>
+    <t>nw</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,17 +107,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:style val="11"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="111"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="11"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -124,13 +152,15 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -145,56 +175,59 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Results_cpu!$A$2:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>ze_gemm</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Results_cpu!$B$2:$B$7</c:f>
+              <c:f>Results_cpu!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>1.07082</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.0708200000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.83126</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.73698</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.42972</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.62065</c:v>
+                  <c:v>0.73697999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.42971999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.62065000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4209-425B-88EB-B155914FAD55}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -210,56 +243,59 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Results_cpu!$A$2:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>ze_gemm</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Results_cpu!$C$2:$C$7</c:f>
+              <c:f>Results_cpu!$C$2:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1.20414</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.87041</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.80697</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.5718800000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.6674</c:v>
+                  <c:v>0.87041000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.80696999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.57188000000000005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.66739999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4209-425B-88EB-B155914FAD55}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -275,56 +311,59 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Results_cpu!$A$2:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>ze_gemm</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Results_cpu!$D$2:$D$7</c:f>
+              <c:f>Results_cpu!$D$2:$D$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1.28861</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8667899999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.80813</c:v>
+                  <c:v>0.86678999999999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.80813000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.48418</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.66726</c:v>
+                  <c:v>0.66725999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4209-425B-88EB-B155914FAD55}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -340,57 +379,69 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Results_cpu!$A$2:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>ze_gemm</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Results_cpu!$E$2:$E$7</c:f>
+              <c:f>Results_cpu!$E$2:$E$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1.29572</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.86698</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.80755</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.58961</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.65844</c:v>
+                  <c:v>0.86697999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.80754999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.58960999999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.65844000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4209-425B-88EB-B155914FAD55}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
       </c:barChart>
@@ -399,6 +450,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -416,20 +468,25 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50010002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -448,9 +505,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
         <c:crosses val="autoZero"/>
@@ -459,9 +518,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -472,9 +533,18 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:style val="12"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="112"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="12"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -492,13 +562,15 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -513,56 +585,59 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Results_cpu!$A$2:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>ze_gemm</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Results_cpu!$F$2:$F$7</c:f>
+              <c:f>Results_cpu!$F$2:$F$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>12.45027175435646</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>12.450271754356461</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>4.709717777831246</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.496865586583082</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>33.08200688820629</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.532425682751946</c:v>
+                  <c:v>9.4968655865830822</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33.082006888206287</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.5324256827519456</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-358E-409C-BC50-8579EE28E222}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -578,56 +653,59 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Results_cpu!$A$2:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>ze_gemm</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Results_cpu!$G$2:$G$7</c:f>
+              <c:f>Results_cpu!$G$2:$G$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>20.33861900225994</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.27423429492577</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.65426470189151</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>12.67336870520339</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.509868686054931</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>20.338619002259939</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.2742342949257699</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.6542647018915098</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.673368705203391</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.5098686860549311</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-358E-409C-BC50-8579EE28E222}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -643,57 +721,69 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Results_cpu!$A$2:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>ze_gemm</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Results_cpu!$H$2:$H$7</c:f>
+              <c:f>Results_cpu!$H$2:$H$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>21.0025961412749</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.297091162813076</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.575565144237295</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>37.20794936237549</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6.088777894143235</c:v>
+                  <c:v>4.2970911628130759</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.5755651442372951</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37.207949362375487</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.0887778941432353</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-358E-409C-BC50-8579EE28E222}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="50020001"/>
         <c:axId val="50020002"/>
       </c:barChart>
@@ -702,6 +792,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -719,20 +810,25 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50020002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -751,9 +847,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
@@ -762,9 +860,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -775,9 +875,18 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:style val="11"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="111"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="11"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -795,13 +904,15 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -816,6 +927,7 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Results_gpu!$A$2:$A$7</c:f>
@@ -825,16 +937,16 @@
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>ze_gemm</c:v>
@@ -849,26 +961,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.44512</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.9174099999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.62168</c:v>
+                  <c:v>0.44512000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.91740999999999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.62168000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1.6819</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.6906</c:v>
+                  <c:v>0.69059999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.46017</c:v>
+                  <c:v>0.46017000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4DBC-4561-AAAA-8E845091BCB3}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -884,6 +1001,7 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Results_gpu!$A$2:$A$7</c:f>
@@ -893,16 +1011,16 @@
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>ze_gemm</c:v>
@@ -920,23 +1038,28 @@
                   <c:v>0.47713</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.95468</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.67588</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.82211</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.7217</c:v>
+                  <c:v>0.95467999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.67588000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.8221099999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.72170000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.52156</c:v>
+                  <c:v>0.52156000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4DBC-4561-AAAA-8E845091BCB3}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -952,6 +1075,7 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Results_gpu!$A$2:$A$7</c:f>
@@ -961,16 +1085,16 @@
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>ze_gemm</c:v>
@@ -985,26 +1109,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.48149</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.95298</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.68491</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.78124</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.71193</c:v>
+                  <c:v>0.48148999999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.95298000000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.68491000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7812399999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.71192999999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.55024</c:v>
+                  <c:v>0.55023999999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4DBC-4561-AAAA-8E845091BCB3}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -1020,6 +1149,7 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Results_gpu!$A$2:$A$7</c:f>
@@ -1029,16 +1159,16 @@
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>ze_gemm</c:v>
@@ -1053,27 +1183,41 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.48772</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.95588</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.6817299999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.85139</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.72421</c:v>
+                  <c:v>0.48771999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.95587999999999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.68172999999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.8513900000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.72421000000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.55818</c:v>
+                  <c:v>0.55818000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4DBC-4561-AAAA-8E845091BCB3}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="50030001"/>
         <c:axId val="50030002"/>
       </c:barChart>
@@ -1082,6 +1226,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -1099,20 +1244,25 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50030002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -1131,9 +1281,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030001"/>
         <c:crosses val="autoZero"/>
@@ -1142,9 +1294,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1155,9 +1309,18 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:style val="12"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="112"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="12"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1175,13 +1338,15 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1196,6 +1361,7 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Results_gpu!$A$2:$A$7</c:f>
@@ -1205,16 +1371,16 @@
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>ze_gemm</c:v>
@@ -1229,19 +1395,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.191319194823864</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.062523844300806</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.71831167159954</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.336405255960518</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.5033304373009</c:v>
+                  <c:v>7.1913191948238637</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.0625238443008058</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.7183116715995403</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.3364052559605177</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.5033304373009004</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>13.34072190712128</c:v>
@@ -1249,6 +1415,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1E33-45A1-80AA-9424061D9538}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1264,6 +1435,7 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Results_gpu!$A$2:$A$7</c:f>
@@ -1273,16 +1445,16 @@
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>ze_gemm</c:v>
@@ -1297,19 +1469,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>8.170830337886404</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.877219563771935</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.17082743533651</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.906415363576906</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.08861859252823</c:v>
+                  <c:v>8.1708303378864038</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.8772195637719351</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.170827435336509</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.9064153635769063</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.0886185925282299</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>19.57320120824911</c:v>
@@ -1317,6 +1489,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1E33-45A1-80AA-9424061D9538}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -1332,6 +1509,7 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Results_gpu!$A$2:$A$7</c:f>
@@ -1341,16 +1519,16 @@
                   <c:v>cl_gemm</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>bench_b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bench_bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bench_gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>bench_nw</c:v>
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>ze_gemm</c:v>
@@ -1365,19 +1543,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>9.570452911574399</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.193326865850602</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.659310256080287</c:v>
+                  <c:v>9.5704529115743995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.1933268658506018</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.6593102560802873</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>10.07729353707118</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.866782507964094</c:v>
+                  <c:v>4.8667825079640936</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>21.29865049872873</c:v>
@@ -1385,7 +1563,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1E33-45A1-80AA-9424061D9538}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="50040001"/>
         <c:axId val="50040002"/>
       </c:barChart>
@@ -1394,6 +1586,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -1411,20 +1604,25 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50040002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50040002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -1443,9 +1641,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50040001"/>
         <c:crosses val="autoZero"/>
@@ -1454,9 +1654,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1483,7 +1685,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1513,7 +1721,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1548,7 +1762,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1578,7 +1798,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1597,9 +1823,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1637,7 +1863,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1671,6 +1897,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1705,9 +1932,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1880,16 +2108,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
     <col min="2" max="5" width="12.7109375" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1915,12 +2143,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
-        <v>1.07082</v>
+        <v>1.0708200000000001</v>
       </c>
       <c r="C2">
         <v>1.20414</v>
@@ -1932,122 +2160,122 @@
         <v>1.29572</v>
       </c>
       <c r="F2">
-        <v>12.45027175435646</v>
+        <v>12.450271754356461</v>
       </c>
       <c r="G2">
-        <v>20.33861900225994</v>
+        <v>20.338619002259939</v>
       </c>
       <c r="H2">
         <v>21.0025961412749</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>0.83126</v>
       </c>
       <c r="C3">
-        <v>0.87041</v>
+        <v>0.87041000000000002</v>
       </c>
       <c r="D3">
-        <v>0.8667899999999999</v>
+        <v>0.86678999999999995</v>
       </c>
       <c r="E3">
-        <v>0.86698</v>
+        <v>0.86697999999999997</v>
       </c>
       <c r="F3">
         <v>4.709717777831246</v>
       </c>
       <c r="G3">
-        <v>4.27423429492577</v>
+        <v>4.2742342949257699</v>
       </c>
       <c r="H3">
-        <v>4.297091162813076</v>
+        <v>4.2970911628130759</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>0.73698</v>
+        <v>0.73697999999999997</v>
       </c>
       <c r="C4">
-        <v>0.80697</v>
+        <v>0.80696999999999997</v>
       </c>
       <c r="D4">
-        <v>0.80813</v>
+        <v>0.80813000000000001</v>
       </c>
       <c r="E4">
-        <v>0.80755</v>
+        <v>0.80754999999999999</v>
       </c>
       <c r="F4">
-        <v>9.496865586583082</v>
+        <v>9.4968655865830822</v>
       </c>
       <c r="G4">
-        <v>9.65426470189151</v>
+        <v>9.6542647018915098</v>
       </c>
       <c r="H4">
-        <v>9.575565144237295</v>
+        <v>9.5755651442372951</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5">
-        <v>0.42972</v>
+        <v>0.42971999999999999</v>
       </c>
       <c r="C5">
-        <v>0.5718800000000001</v>
+        <v>0.57188000000000005</v>
       </c>
       <c r="D5">
         <v>0.48418</v>
       </c>
       <c r="E5">
-        <v>0.58961</v>
+        <v>0.58960999999999997</v>
       </c>
       <c r="F5">
-        <v>33.08200688820629</v>
+        <v>33.082006888206287</v>
       </c>
       <c r="G5">
-        <v>12.67336870520339</v>
+        <v>12.673368705203391</v>
       </c>
       <c r="H5">
-        <v>37.20794936237549</v>
+        <v>37.207949362375487</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6">
-        <v>0.62065</v>
+        <v>0.62065000000000003</v>
       </c>
       <c r="C6">
-        <v>0.6674</v>
+        <v>0.66739999999999999</v>
       </c>
       <c r="D6">
-        <v>0.66726</v>
+        <v>0.66725999999999996</v>
       </c>
       <c r="E6">
-        <v>0.65844</v>
+        <v>0.65844000000000003</v>
       </c>
       <c r="F6">
-        <v>7.532425682751946</v>
+        <v>7.5324256827519456</v>
       </c>
       <c r="G6">
-        <v>7.509868686054931</v>
+        <v>7.5098686860549311</v>
       </c>
       <c r="H6">
-        <v>6.088777894143235</v>
+        <v>6.0887778941432353</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2057,16 +2285,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
     <col min="2" max="5" width="12.7109375" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2092,151 +2320,151 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.44512</v>
+        <v>0.44512000000000002</v>
       </c>
       <c r="C2">
         <v>0.47713</v>
       </c>
       <c r="D2">
-        <v>0.48149</v>
+        <v>0.48148999999999997</v>
       </c>
       <c r="E2">
-        <v>0.48772</v>
+        <v>0.48771999999999999</v>
       </c>
       <c r="F2">
-        <v>7.191319194823864</v>
+        <v>7.1913191948238637</v>
       </c>
       <c r="G2">
-        <v>8.170830337886404</v>
+        <v>8.1708303378864038</v>
       </c>
       <c r="H2">
-        <v>9.570452911574399</v>
+        <v>9.5704529115743995</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>0.9174099999999999</v>
+        <v>0.91740999999999995</v>
       </c>
       <c r="C3">
-        <v>0.95468</v>
+        <v>0.95467999999999997</v>
       </c>
       <c r="D3">
-        <v>0.95298</v>
+        <v>0.95298000000000005</v>
       </c>
       <c r="E3">
-        <v>0.95588</v>
+        <v>0.95587999999999995</v>
       </c>
       <c r="F3">
-        <v>4.062523844300806</v>
+        <v>4.0625238443008058</v>
       </c>
       <c r="G3">
-        <v>3.877219563771935</v>
+        <v>3.8772195637719351</v>
       </c>
       <c r="H3">
-        <v>4.193326865850602</v>
+        <v>4.1933268658506018</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>0.62168</v>
+        <v>0.62168000000000001</v>
       </c>
       <c r="C4">
-        <v>0.67588</v>
+        <v>0.67588000000000004</v>
       </c>
       <c r="D4">
-        <v>0.68491</v>
+        <v>0.68491000000000002</v>
       </c>
       <c r="E4">
-        <v>0.6817299999999999</v>
+        <v>0.68172999999999995</v>
       </c>
       <c r="F4">
-        <v>8.71831167159954</v>
+        <v>8.7183116715995403</v>
       </c>
       <c r="G4">
-        <v>10.17082743533651</v>
+        <v>10.170827435336509</v>
       </c>
       <c r="H4">
-        <v>9.659310256080287</v>
+        <v>9.6593102560802873</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>1.6819</v>
       </c>
       <c r="C5">
-        <v>1.82211</v>
+        <v>1.8221099999999999</v>
       </c>
       <c r="D5">
-        <v>1.78124</v>
+        <v>1.7812399999999999</v>
       </c>
       <c r="E5">
-        <v>1.85139</v>
+        <v>1.8513900000000001</v>
       </c>
       <c r="F5">
-        <v>8.336405255960518</v>
+        <v>8.3364052559605177</v>
       </c>
       <c r="G5">
-        <v>5.906415363576906</v>
+        <v>5.9064153635769063</v>
       </c>
       <c r="H5">
         <v>10.07729353707118</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6">
-        <v>0.6906</v>
+        <v>0.69059999999999999</v>
       </c>
       <c r="C6">
-        <v>0.7217</v>
+        <v>0.72170000000000001</v>
       </c>
       <c r="D6">
-        <v>0.71193</v>
+        <v>0.71192999999999995</v>
       </c>
       <c r="E6">
-        <v>0.72421</v>
+        <v>0.72421000000000002</v>
       </c>
       <c r="F6">
-        <v>4.5033304373009</v>
+        <v>4.5033304373009004</v>
       </c>
       <c r="G6">
-        <v>3.08861859252823</v>
+        <v>3.0886185925282299</v>
       </c>
       <c r="H6">
-        <v>4.866782507964094</v>
+        <v>4.8667825079640936</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>0.46017</v>
+        <v>0.46017000000000002</v>
       </c>
       <c r="C7">
-        <v>0.52156</v>
+        <v>0.52156000000000002</v>
       </c>
       <c r="D7">
-        <v>0.55024</v>
+        <v>0.55023999999999995</v>
       </c>
       <c r="E7">
-        <v>0.55818</v>
+        <v>0.55818000000000001</v>
       </c>
       <c r="F7">
         <v>13.34072190712128</v>

--- a/finetrace_overhead_stat.xlsx
+++ b/finetrace_overhead_stat.xlsx
@@ -1,32 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\FineTrace\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B2C6F1C-49DE-4933-94CF-BE97552F8D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Results_cpu" sheetId="1" r:id="rId1"/>
     <sheet name="Results_gpu" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
   <si>
     <t>Benchmark</t>
   </si>
@@ -34,28 +23,37 @@
     <t>clean</t>
   </si>
   <si>
+    <t>host-timing</t>
+  </si>
+  <si>
     <t>call-logging</t>
   </si>
   <si>
-    <t>device-timeline</t>
+    <t>host+call</t>
   </si>
   <si>
-    <t>both</t>
+    <t>metrics</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>host-timing (%)</t>
   </si>
   <si>
     <t>call-logging (%)</t>
   </si>
   <si>
-    <t>device-timeline (%)</t>
+    <t>host+call (%)</t>
   </si>
   <si>
-    <t>both (%)</t>
+    <t>metrics (%)</t>
+  </si>
+  <si>
+    <t>all (%)</t>
   </si>
   <si>
     <t>cl_gemm</t>
-  </si>
-  <si>
-    <t>ze_gemm</t>
   </si>
   <si>
     <t>b+tree</t>
@@ -69,12 +67,15 @@
   <si>
     <t>nw</t>
   </si>
+  <si>
+    <t>ze_gemm</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,34 +108,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="111"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="11"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:style val="11"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -147,20 +131,18 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Absolute Time - CPU</a:t>
+              <a:t>Время выполнения — CPU</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -175,7 +157,16 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="D6E4F5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="D6E4F5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
           <c:cat>
             <c:strRef>
               <c:f>Results_cpu!$A$2:$A$6</c:f>
@@ -206,28 +197,23 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.0708200000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.83126</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.73697999999999997</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.42971999999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.62065000000000003</c:v>
+                  <c:v>1.1939</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8384200000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.74368</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.41028</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.58324</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4209-425B-88EB-B155914FAD55}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -238,12 +224,21 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>call-logging</c:v>
+                  <c:v>host-timing</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="A8C8EC"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="A8C8EC"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
           <c:cat>
             <c:strRef>
               <c:f>Results_cpu!$A$2:$A$6</c:f>
@@ -274,28 +269,23 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.20414</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.87041000000000002</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.80696999999999997</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.57188000000000005</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.66739999999999999</c:v>
+                  <c:v>1.35776</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.87608</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8079</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.46479</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.609</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4209-425B-88EB-B155914FAD55}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -306,12 +296,21 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device-timeline</c:v>
+                  <c:v>call-logging</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="74A9DE"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="74A9DE"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
           <c:cat>
             <c:strRef>
               <c:f>Results_cpu!$A$2:$A$6</c:f>
@@ -342,28 +341,23 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.28861</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.86678999999999995</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.80813000000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.48418</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.66725999999999996</c:v>
+                  <c:v>1.3698</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.87408</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.82147</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.60193</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.61386</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-4209-425B-88EB-B155914FAD55}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -374,12 +368,21 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>both</c:v>
+                  <c:v>host+call</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4080C8"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="4080C8"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
           <c:cat>
             <c:strRef>
               <c:f>Results_cpu!$A$2:$A$6</c:f>
@@ -410,38 +413,138 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.29572</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.86697999999999997</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.80754999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.58960999999999997</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.65844000000000003</c:v>
+                  <c:v>1.38552</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.87698</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8212</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.59901</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.60997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-4209-425B-88EB-B155914FAD55}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Results_cpu!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>metrics</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F5BAF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="1F5BAF"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Results_cpu!$F$2:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Results_cpu!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>all</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="0D3478"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="0D3478"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Results_cpu!$G$2:$G$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
       </c:barChart>
@@ -450,7 +553,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -463,30 +565,25 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Benchmark</a:t>
+                  <a:t>Приложение</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50010002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -500,16 +597,14 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Time (s)</a:t>
+                  <a:t>Время (с)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
         <c:crosses val="autoZero"/>
@@ -518,11 +613,9 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -533,18 +626,9 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="112"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="12"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:style val="12"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -557,171 +641,42 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Overhead Percentage - CPU</a:t>
+              <a:t>Накладные расходы vs clean — CPU</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Results_cpu!$F$1</c:f>
+              <c:f>Results_cpu!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>call-logging (%)</c:v>
+                  <c:v>host-timing (%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Results_cpu!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>cl_gemm</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>nw</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Results_cpu!$F$2:$F$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>12.450271754356461</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.709717777831246</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.4968655865830822</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>33.082006888206287</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.5324256827519456</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-358E-409C-BC50-8579EE28E222}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Results_cpu!$G$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>device-timeline (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Results_cpu!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>cl_gemm</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>nw</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Results_cpu!$G$2:$G$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>20.338619002259939</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.2742342949257699</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.6542647018915098</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>12.673368705203391</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.5098686860549311</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-358E-409C-BC50-8579EE28E222}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Results_cpu!$H$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>both (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:invertIfNegative val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="D6E4F5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="D6E4F5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
           <c:cat>
             <c:strRef>
               <c:f>Results_cpu!$A$2:$A$6</c:f>
@@ -752,38 +707,282 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>21.0025961412749</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.2970911628130759</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.5755651442372951</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>37.207949362375487</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6.0887778941432353</c:v>
+                  <c:v>13.72476756847308</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.491782161685063</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.635434595524949</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13.28604855220825</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.416706673067692</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-358E-409C-BC50-8579EE28E222}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Results_cpu!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>call-logging (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="A8C8EC"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="A8C8EC"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Results_cpu!$I$2:$I$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>14.73322723846218</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.253238233820747</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.46014414802066</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46.71200155991031</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.249982854399557</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Results_cpu!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>host+call (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="74A9DE"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="74A9DE"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Results_cpu!$J$2:$J$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>16.04992042884665</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.599126929224007</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.42383820998279</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46.00029248318224</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.583018997325292</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Results_cpu!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>metrics (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F5BAF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="1F5BAF"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Results_cpu!$K$2:$K$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Results_cpu!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>all (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="0D3478"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="0D3478"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Results_cpu!$L$2:$L$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
         <c:axId val="50020001"/>
         <c:axId val="50020002"/>
       </c:barChart>
@@ -792,7 +991,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -805,30 +1003,25 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Benchmark</a:t>
+                  <a:t>Приложение</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50020002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -842,16 +1035,14 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Overhead (%)</a:t>
+                  <a:t>Накладные расходы (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
@@ -860,11 +1051,9 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -875,18 +1064,9 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="111"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="11"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:style val="11"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -899,20 +1079,18 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Absolute Time - GPU</a:t>
+              <a:t>Время выполнения — GPU</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -927,7 +1105,16 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="D6E4F5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="D6E4F5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
           <c:cat>
             <c:strRef>
               <c:f>Results_gpu!$A$2:$A$7</c:f>
@@ -961,31 +1148,26 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.44512000000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.91740999999999995</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.62168000000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.6819</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.69059999999999999</c:v>
+                  <c:v>0.37274</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94203</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.63866</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.43401</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.6906</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.46017000000000002</c:v>
+                  <c:v>0.38645</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4DBC-4561-AAAA-8E845091BCB3}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -996,12 +1178,21 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>call-logging</c:v>
+                  <c:v>host-timing</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="A8C8EC"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="A8C8EC"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
           <c:cat>
             <c:strRef>
               <c:f>Results_gpu!$A$2:$A$7</c:f>
@@ -1035,31 +1226,26 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.47713</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.95467999999999997</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.67588000000000004</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.8221099999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.72170000000000001</c:v>
+                  <c:v>0.40226</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96063</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69172</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.47491</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.65367</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.52156000000000002</c:v>
+                  <c:v>0.43977</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4DBC-4561-AAAA-8E845091BCB3}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -1070,12 +1256,21 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>device-timeline</c:v>
+                  <c:v>call-logging</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="74A9DE"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="74A9DE"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
           <c:cat>
             <c:strRef>
               <c:f>Results_gpu!$A$2:$A$7</c:f>
@@ -1109,31 +1304,26 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.48148999999999997</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.95298000000000005</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.68491000000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.7812399999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.71192999999999995</c:v>
+                  <c:v>0.40869</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.95679</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69535</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.53855</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.65915</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.55023999999999995</c:v>
+                  <c:v>0.44166</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-4DBC-4561-AAAA-8E845091BCB3}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -1144,12 +1334,21 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>both</c:v>
+                  <c:v>host+call</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4080C8"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="4080C8"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
           <c:cat>
             <c:strRef>
               <c:f>Results_gpu!$A$2:$A$7</c:f>
@@ -1183,41 +1382,183 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.48771999999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.95587999999999995</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.68172999999999995</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.8513900000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.72421000000000002</c:v>
+                  <c:v>0.40704</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.95424</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69321</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.53651</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.6523600000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.55818000000000001</c:v>
+                  <c:v>0.44779</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-4DBC-4561-AAAA-8E845091BCB3}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Results_gpu!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>metrics</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F5BAF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="1F5BAF"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_gpu!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>ze_gemm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Results_gpu!$F$2:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.61185</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1511</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.87485</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.90899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.84053</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.65926</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Results_gpu!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>all</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="0D3478"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="0D3478"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_gpu!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>ze_gemm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Results_gpu!$G$2:$G$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.62443</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.15575</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.88347</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.02937</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.84519</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.67709</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
         <c:axId val="50030001"/>
         <c:axId val="50030002"/>
       </c:barChart>
@@ -1226,7 +1567,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -1239,30 +1579,25 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Benchmark</a:t>
+                  <a:t>Приложение</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50030002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -1276,16 +1611,14 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Time (s)</a:t>
+                  <a:t>Время (с)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030001"/>
         <c:crosses val="autoZero"/>
@@ -1294,11 +1627,9 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1309,18 +1640,9 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="112"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="12"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:style val="12"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1333,183 +1655,42 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Overhead Percentage - GPU</a:t>
+              <a:t>Накладные расходы vs clean — GPU</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Results_gpu!$F$1</c:f>
+              <c:f>Results_gpu!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>call-logging (%)</c:v>
+                  <c:v>host-timing (%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Results_gpu!$A$2:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>cl_gemm</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>nw</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>ze_gemm</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Results_gpu!$F$2:$F$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>7.1913191948238637</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.0625238443008058</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.7183116715995403</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.3364052559605177</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.5033304373009004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>13.34072190712128</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1E33-45A1-80AA-9424061D9538}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Results_gpu!$G$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>device-timeline (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Results_gpu!$A$2:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>cl_gemm</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>nw</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>ze_gemm</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Results_gpu!$G$2:$G$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>8.1708303378864038</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.8772195637719351</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.170827435336509</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.9064153635769063</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.0886185925282299</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>19.57320120824911</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-1E33-45A1-80AA-9424061D9538}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Results_gpu!$H$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>both (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:invertIfNegative val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="D6E4F5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="D6E4F5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
           <c:cat>
             <c:strRef>
               <c:f>Results_gpu!$A$2:$A$7</c:f>
@@ -1543,41 +1724,339 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>9.5704529115743995</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.1933268658506018</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.6593102560802873</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.07729353707118</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.8667825079640936</c:v>
+                  <c:v>7.919729570209795</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.974459412120628</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.308019916700591</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.852141895802675</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-5.347523892267596</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>21.29865049872873</c:v>
+                  <c:v>13.79738646655453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-1E33-45A1-80AA-9424061D9538}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Results_gpu!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>call-logging (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="A8C8EC"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="A8C8EC"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_gpu!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>ze_gemm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Results_gpu!$I$2:$I$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>9.644792616837469</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.566829081876373</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.876397457175965</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.290046791863382</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4.554011004923252</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14.28645361625048</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Results_gpu!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>host+call (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="74A9DE"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="74A9DE"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_gpu!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>ze_gemm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Results_gpu!$J$2:$J$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>9.202124805494446</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.296137065698539</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.541320890614724</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.147788369676642</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-5.537214016796979</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15.87268728166645</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Results_gpu!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>metrics (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F5BAF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="1F5BAF"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_gpu!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>ze_gemm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Results_gpu!$K$2:$K$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>64.14927295165531</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.19356071462692</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36.98211881126107</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33.12250263247815</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>21.71010715320012</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70.59386725320221</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Results_gpu!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>all (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="0D3478"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="0D3478"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_gpu!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>ze_gemm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Results_gpu!$L$2:$L$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>67.52427965874337</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.68717556765708</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38.33181974759653</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>41.51714423190913</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22.38488271068636</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>75.20765946435502</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
         <c:axId val="50040001"/>
         <c:axId val="50040002"/>
       </c:barChart>
@@ -1586,7 +2065,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -1599,30 +2077,25 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Benchmark</a:t>
+                  <a:t>Приложение</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50040002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50040002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -1636,16 +2109,14 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Overhead (%)</a:t>
+                  <a:t>Накладные расходы (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50040001"/>
         <c:crosses val="autoZero"/>
@@ -1654,11 +2125,9 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1672,26 +2141,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>895350</xdr:colOff>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1708,26 +2171,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>895350</xdr:colOff>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1749,26 +2206,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>895350</xdr:colOff>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1785,26 +2236,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>895350</xdr:colOff>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1823,9 +2268,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1863,7 +2308,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1897,7 +2342,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1932,10 +2376,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2108,16 +2551,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="8" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="12" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2142,140 +2585,147 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B2">
-        <v>1.0708200000000001</v>
+        <v>1.1939</v>
       </c>
       <c r="C2">
-        <v>1.20414</v>
+        <v>1.35776</v>
       </c>
       <c r="D2">
-        <v>1.28861</v>
+        <v>1.3698</v>
       </c>
       <c r="E2">
-        <v>1.29572</v>
-      </c>
-      <c r="F2">
-        <v>12.450271754356461</v>
-      </c>
-      <c r="G2">
-        <v>20.338619002259939</v>
+        <v>1.38552</v>
       </c>
       <c r="H2">
-        <v>21.0025961412749</v>
+        <v>13.72476756847308</v>
+      </c>
+      <c r="I2">
+        <v>14.73322723846218</v>
+      </c>
+      <c r="J2">
+        <v>16.04992042884665</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3">
-        <v>0.83126</v>
+        <v>0.8384200000000001</v>
       </c>
       <c r="C3">
-        <v>0.87041000000000002</v>
+        <v>0.87608</v>
       </c>
       <c r="D3">
-        <v>0.86678999999999995</v>
+        <v>0.87408</v>
       </c>
       <c r="E3">
-        <v>0.86697999999999997</v>
-      </c>
-      <c r="F3">
-        <v>4.709717777831246</v>
-      </c>
-      <c r="G3">
-        <v>4.2742342949257699</v>
+        <v>0.87698</v>
       </c>
       <c r="H3">
-        <v>4.2970911628130759</v>
+        <v>4.491782161685063</v>
+      </c>
+      <c r="I3">
+        <v>4.253238233820747</v>
+      </c>
+      <c r="J3">
+        <v>4.599126929224007</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4">
-        <v>0.73697999999999997</v>
+        <v>0.74368</v>
       </c>
       <c r="C4">
-        <v>0.80696999999999997</v>
+        <v>0.8079</v>
       </c>
       <c r="D4">
-        <v>0.80813000000000001</v>
+        <v>0.82147</v>
       </c>
       <c r="E4">
-        <v>0.80754999999999999</v>
-      </c>
-      <c r="F4">
-        <v>9.4968655865830822</v>
-      </c>
-      <c r="G4">
-        <v>9.6542647018915098</v>
+        <v>0.8212</v>
       </c>
       <c r="H4">
-        <v>9.5755651442372951</v>
+        <v>8.635434595524949</v>
+      </c>
+      <c r="I4">
+        <v>10.46014414802066</v>
+      </c>
+      <c r="J4">
+        <v>10.42383820998279</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5">
-        <v>0.42971999999999999</v>
+        <v>0.41028</v>
       </c>
       <c r="C5">
-        <v>0.57188000000000005</v>
+        <v>0.46479</v>
       </c>
       <c r="D5">
-        <v>0.48418</v>
+        <v>0.60193</v>
       </c>
       <c r="E5">
-        <v>0.58960999999999997</v>
-      </c>
-      <c r="F5">
-        <v>33.082006888206287</v>
-      </c>
-      <c r="G5">
-        <v>12.673368705203391</v>
+        <v>0.59901</v>
       </c>
       <c r="H5">
-        <v>37.207949362375487</v>
+        <v>13.28604855220825</v>
+      </c>
+      <c r="I5">
+        <v>46.71200155991031</v>
+      </c>
+      <c r="J5">
+        <v>46.00029248318224</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6">
-        <v>0.62065000000000003</v>
+        <v>0.58324</v>
       </c>
       <c r="C6">
-        <v>0.66739999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="D6">
-        <v>0.66725999999999996</v>
+        <v>0.61386</v>
       </c>
       <c r="E6">
-        <v>0.65844000000000003</v>
-      </c>
-      <c r="F6">
-        <v>7.5324256827519456</v>
-      </c>
-      <c r="G6">
-        <v>7.5098686860549311</v>
+        <v>0.60997</v>
       </c>
       <c r="H6">
-        <v>6.0887778941432353</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>9</v>
+        <v>4.416706673067692</v>
+      </c>
+      <c r="I6">
+        <v>5.249982854399557</v>
+      </c>
+      <c r="J6">
+        <v>4.583018997325292</v>
       </c>
     </row>
   </sheetData>
@@ -2285,16 +2735,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="8" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="12" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2319,161 +2769,245 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B2">
-        <v>0.44512000000000002</v>
+        <v>0.37274</v>
       </c>
       <c r="C2">
-        <v>0.47713</v>
+        <v>0.40226</v>
       </c>
       <c r="D2">
-        <v>0.48148999999999997</v>
+        <v>0.40869</v>
       </c>
       <c r="E2">
-        <v>0.48771999999999999</v>
+        <v>0.40704</v>
       </c>
       <c r="F2">
-        <v>7.1913191948238637</v>
+        <v>0.61185</v>
       </c>
       <c r="G2">
-        <v>8.1708303378864038</v>
+        <v>0.62443</v>
       </c>
       <c r="H2">
-        <v>9.5704529115743995</v>
+        <v>7.919729570209795</v>
+      </c>
+      <c r="I2">
+        <v>9.644792616837469</v>
+      </c>
+      <c r="J2">
+        <v>9.202124805494446</v>
+      </c>
+      <c r="K2">
+        <v>64.14927295165531</v>
+      </c>
+      <c r="L2">
+        <v>67.52427965874337</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3">
-        <v>0.91740999999999995</v>
+        <v>0.94203</v>
       </c>
       <c r="C3">
-        <v>0.95467999999999997</v>
+        <v>0.96063</v>
       </c>
       <c r="D3">
-        <v>0.95298000000000005</v>
+        <v>0.95679</v>
       </c>
       <c r="E3">
-        <v>0.95587999999999995</v>
+        <v>0.95424</v>
       </c>
       <c r="F3">
-        <v>4.0625238443008058</v>
+        <v>1.1511</v>
       </c>
       <c r="G3">
-        <v>3.8772195637719351</v>
+        <v>1.15575</v>
       </c>
       <c r="H3">
-        <v>4.1933268658506018</v>
+        <v>1.974459412120628</v>
+      </c>
+      <c r="I3">
+        <v>1.566829081876373</v>
+      </c>
+      <c r="J3">
+        <v>1.296137065698539</v>
+      </c>
+      <c r="K3">
+        <v>22.19356071462692</v>
+      </c>
+      <c r="L3">
+        <v>22.68717556765708</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4">
-        <v>0.62168000000000001</v>
+        <v>0.63866</v>
       </c>
       <c r="C4">
-        <v>0.67588000000000004</v>
+        <v>0.69172</v>
       </c>
       <c r="D4">
-        <v>0.68491000000000002</v>
+        <v>0.69535</v>
       </c>
       <c r="E4">
-        <v>0.68172999999999995</v>
+        <v>0.69321</v>
       </c>
       <c r="F4">
-        <v>8.7183116715995403</v>
+        <v>0.87485</v>
       </c>
       <c r="G4">
-        <v>10.170827435336509</v>
+        <v>0.88347</v>
       </c>
       <c r="H4">
-        <v>9.6593102560802873</v>
+        <v>8.308019916700591</v>
+      </c>
+      <c r="I4">
+        <v>8.876397457175965</v>
+      </c>
+      <c r="J4">
+        <v>8.541320890614724</v>
+      </c>
+      <c r="K4">
+        <v>36.98211881126107</v>
+      </c>
+      <c r="L4">
+        <v>38.33181974759653</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5">
-        <v>1.6819</v>
+        <v>1.43401</v>
       </c>
       <c r="C5">
-        <v>1.8221099999999999</v>
+        <v>1.47491</v>
       </c>
       <c r="D5">
-        <v>1.7812399999999999</v>
+        <v>1.53855</v>
       </c>
       <c r="E5">
-        <v>1.8513900000000001</v>
+        <v>1.53651</v>
       </c>
       <c r="F5">
-        <v>8.3364052559605177</v>
+        <v>1.90899</v>
       </c>
       <c r="G5">
-        <v>5.9064153635769063</v>
+        <v>2.02937</v>
       </c>
       <c r="H5">
-        <v>10.07729353707118</v>
+        <v>2.852141895802675</v>
+      </c>
+      <c r="I5">
+        <v>7.290046791863382</v>
+      </c>
+      <c r="J5">
+        <v>7.147788369676642</v>
+      </c>
+      <c r="K5">
+        <v>33.12250263247815</v>
+      </c>
+      <c r="L5">
+        <v>41.51714423190913</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6">
-        <v>0.69059999999999999</v>
+        <v>0.6906</v>
       </c>
       <c r="C6">
-        <v>0.72170000000000001</v>
+        <v>0.65367</v>
       </c>
       <c r="D6">
-        <v>0.71192999999999995</v>
+        <v>0.65915</v>
       </c>
       <c r="E6">
-        <v>0.72421000000000002</v>
+        <v>0.6523600000000001</v>
       </c>
       <c r="F6">
-        <v>4.5033304373009004</v>
+        <v>0.84053</v>
       </c>
       <c r="G6">
-        <v>3.0886185925282299</v>
+        <v>0.84519</v>
       </c>
       <c r="H6">
-        <v>4.8667825079640936</v>
+        <v>-5.347523892267596</v>
+      </c>
+      <c r="I6">
+        <v>-4.554011004923252</v>
+      </c>
+      <c r="J6">
+        <v>-5.537214016796979</v>
+      </c>
+      <c r="K6">
+        <v>21.71010715320012</v>
+      </c>
+      <c r="L6">
+        <v>22.38488271068636</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B7">
-        <v>0.46017000000000002</v>
+        <v>0.38645</v>
       </c>
       <c r="C7">
-        <v>0.52156000000000002</v>
+        <v>0.43977</v>
       </c>
       <c r="D7">
-        <v>0.55023999999999995</v>
+        <v>0.44166</v>
       </c>
       <c r="E7">
-        <v>0.55818000000000001</v>
+        <v>0.44779</v>
       </c>
       <c r="F7">
-        <v>13.34072190712128</v>
+        <v>0.65926</v>
       </c>
       <c r="G7">
-        <v>19.57320120824911</v>
+        <v>0.67709</v>
       </c>
       <c r="H7">
-        <v>21.29865049872873</v>
+        <v>13.79738646655453</v>
+      </c>
+      <c r="I7">
+        <v>14.28645361625048</v>
+      </c>
+      <c r="J7">
+        <v>15.87268728166645</v>
+      </c>
+      <c r="K7">
+        <v>70.59386725320221</v>
+      </c>
+      <c r="L7">
+        <v>75.20765946435502</v>
       </c>
     </row>
   </sheetData>

--- a/finetrace_overhead_stat.xlsx
+++ b/finetrace_overhead_stat.xlsx
@@ -147,15 +147,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_cpu!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>clean</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Обычный запуск</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -197,19 +189,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.1939</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.8384200000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.74368</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.41028</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.58324</c:v>
+                  <c:v>1.1435</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.83871</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.74134</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.42139</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.57596</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -219,15 +211,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_cpu!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>host-timing</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace: хост-тайминг (1)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -269,19 +253,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.35776</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.87608</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.8079</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.46479</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.609</c:v>
+                  <c:v>1.39718</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.87695</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.82117</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.47398</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.60729</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -291,15 +275,7 @@
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_cpu!$D$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>call-logging</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace: трейсинг вызовов (2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -341,19 +317,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.3698</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.87408</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.82147</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.60193</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.61386</c:v>
+                  <c:v>1.39223</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.87287</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.82345</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.60687</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.60826</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -363,15 +339,7 @@
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_cpu!$E$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>host+call</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace (1)+(2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -413,19 +381,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.38552</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.87698</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.8212</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.59901</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.60997</c:v>
+                  <c:v>1.44656</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.87659</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.82152</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.60553</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.60528</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -435,15 +403,7 @@
           <c:idx val="4"/>
           <c:order val="4"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_cpu!$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>metrics</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace: метрики GPU (3)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -492,15 +452,7 @@
           <c:idx val="5"/>
           <c:order val="5"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_cpu!$G$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>all</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace (1)+(2)+(3)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -612,7 +564,7 @@
       </c:valAx>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
       <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -657,87 +609,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_cpu!$H$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>host-timing (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="D6E4F5"/>
-            </a:solidFill>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="D6E4F5"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:cat>
-            <c:strRef>
-              <c:f>Results_cpu!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>cl_gemm</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>nw</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Results_cpu!$H$2:$H$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>13.72476756847308</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.491782161685063</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.635434595524949</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>13.28604855220825</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.416706673067692</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Results_cpu!$I$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>call-logging (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace: хост-тайминг (1)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -774,42 +646,34 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Results_cpu!$I$2:$I$6</c:f>
+              <c:f>Results_cpu!$H$2:$H$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>14.73322723846218</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.253238233820747</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.46014414802066</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>46.71200155991031</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.249982854399557</c:v>
+                  <c:v>22.18452120682118</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.559382861775829</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.76833841422289</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.4801252996037</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.439613862073749</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Results_cpu!$J$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>host+call (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>FineTrace: трейсинг вызовов (2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -846,24 +710,88 @@
           </c:cat>
           <c:val>
             <c:numRef>
+              <c:f>Results_cpu!$I$2:$I$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>21.75163970266726</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.072921510414814</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.07588960530931</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44.01623199411473</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.608028335301062</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>FineTrace (1)+(2)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4080C8"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="4080C8"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_cpu!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
               <c:f>Results_cpu!$J$2:$J$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>16.04992042884665</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.599126929224007</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.42383820998279</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>46.00029248318224</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.583018997325292</c:v>
+                  <c:v>26.50284215128991</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.516459801361618</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.81555021987213</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43.6982367877738</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.090631293839852</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -873,15 +801,7 @@
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_cpu!$K$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>metrics (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace: метрики GPU (3)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -930,15 +850,7 @@
           <c:idx val="4"/>
           <c:order val="4"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_cpu!$L$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>all (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace (1)+(2)+(3)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1050,7 +962,7 @@
       </c:valAx>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
       <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -1095,15 +1007,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_gpu!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>clean</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Обычный запуск</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1148,22 +1052,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.37274</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.94203</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.63866</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.43401</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.6906</c:v>
+                  <c:v>0.36925</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.9402700000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.63531</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.45088</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.65083</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.38645</c:v>
+                  <c:v>0.38339</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1173,15 +1077,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_gpu!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>host-timing</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace: хост-тайминг (1)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1226,22 +1122,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.40226</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.96063</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.69172</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.47491</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.65367</c:v>
+                  <c:v>0.39533</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96545</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.70186</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.48913</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.63658</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.43977</c:v>
+                  <c:v>0.43824</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1251,15 +1147,7 @@
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_gpu!$D$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>call-logging</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace: трейсинг вызовов (2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1304,22 +1192,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.40869</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.95679</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.69535</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.53855</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.65915</c:v>
+                  <c:v>0.40007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96543</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69881</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.55071</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.63914</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.44166</c:v>
+                  <c:v>0.44397</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1329,15 +1217,7 @@
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_gpu!$E$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>host+call</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace (1)+(2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1382,22 +1262,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.40704</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.95424</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.69321</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.53651</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.6523600000000001</c:v>
+                  <c:v>0.40222</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.9638</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69853</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.55158</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.63974</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.44779</c:v>
+                  <c:v>0.44632</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1407,15 +1287,7 @@
           <c:idx val="4"/>
           <c:order val="4"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_gpu!$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>metrics</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace: метрики GPU (3)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1460,22 +1332,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.61185</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.1511</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.87485</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.90899</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.84053</c:v>
+                  <c:v>0.60908</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.14668</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.86689</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.90653</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.82348</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.65926</c:v>
+                  <c:v>0.6571</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1485,15 +1357,7 @@
           <c:idx val="5"/>
           <c:order val="5"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_gpu!$G$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>all</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace (1)+(2)+(3)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1538,22 +1402,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.62443</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.15575</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.88347</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.02937</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.84519</c:v>
+                  <c:v>0.60975</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.15959</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8817199999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.0111</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.83275</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.67709</c:v>
+                  <c:v>0.6764</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1626,7 +1490,7 @@
       </c:valAx>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
       <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -1671,93 +1535,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_gpu!$H$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>host-timing (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="D6E4F5"/>
-            </a:solidFill>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="D6E4F5"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:cat>
-            <c:strRef>
-              <c:f>Results_gpu!$A$2:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>cl_gemm</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>b+tree</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>bfs</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>gaussian</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>nw</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>ze_gemm</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Results_gpu!$H$2:$H$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>7.919729570209795</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.974459412120628</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.308019916700591</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.852141895802675</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-5.347523892267596</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>13.79738646655453</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Results_gpu!$I$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>call-logging (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace: хост-тайминг (1)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1797,45 +1575,37 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Results_gpu!$I$2:$I$7</c:f>
+              <c:f>Results_gpu!$H$2:$H$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>9.644792616837469</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.566829081876373</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.876397457175965</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.290046791863382</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-4.554011004923252</c:v>
+                  <c:v>7.062965470548406</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.677954204643345</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.47520108293589</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.636331054256735</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2.189511854094</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.28645361625048</c:v>
+                  <c:v>14.3065807663215</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Results_gpu!$J$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>host+call (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>FineTrace: трейсинг вызовов (2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1875,27 +1645,97 @@
           </c:cat>
           <c:val>
             <c:numRef>
+              <c:f>Results_gpu!$I$2:$I$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>8.346648612051444</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.675827156029646</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.99512049235806</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.880651742390831</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.796167970130445</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15.80114243981324</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>FineTrace (1)+(2)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4080C8"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="4080C8"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Results_gpu!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>cl_gemm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>b+tree</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bfs</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gaussian</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>nw</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>ze_gemm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
               <c:f>Results_gpu!$J$2:$J$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>9.202124805494446</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.296137065698539</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.541320890614724</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.147788369676642</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-5.537214016796979</c:v>
+                  <c:v>8.928909952606634</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.502472694013415</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.951047520108284</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.940615350683724</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.703977997326498</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>15.87268728166645</c:v>
+                  <c:v>16.41409530765017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1905,15 +1745,7 @@
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_gpu!$K$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>metrics (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace: метрики GPU (3)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1958,22 +1790,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>64.14927295165531</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>22.19356071462692</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>36.98211881126107</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>33.12250263247815</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>21.71010715320012</c:v>
+                  <c:v>64.95057549085983</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.95220521765023</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36.45149612000441</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31.40507829730923</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26.52766467433892</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>70.59386725320221</c:v>
+                  <c:v>71.39205508750879</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1983,15 +1815,7 @@
           <c:idx val="4"/>
           <c:order val="4"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Results_gpu!$L$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>all (%)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>FineTrace (1)+(2)+(3)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -2036,22 +1860,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>67.52427965874337</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>22.68717556765708</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>38.33181974759653</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>41.51714423190913</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>22.38488271068636</c:v>
+                  <c:v>65.13202437373053</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23.32521509779104</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38.78578961451888</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38.6124283193648</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>27.95199975416007</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>75.20765946435502</c:v>
+                  <c:v>76.42609353399932</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2124,7 +1948,7 @@
       </c:valAx>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
       <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -2149,8 +1973,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>895350</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2173,14 +1997,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>895350</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2214,8 +2038,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>895350</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2238,14 +2062,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>895350</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2603,25 +2427,25 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>1.1939</v>
+        <v>1.1435</v>
       </c>
       <c r="C2">
-        <v>1.35776</v>
+        <v>1.39718</v>
       </c>
       <c r="D2">
-        <v>1.3698</v>
+        <v>1.39223</v>
       </c>
       <c r="E2">
-        <v>1.38552</v>
+        <v>1.44656</v>
       </c>
       <c r="H2">
-        <v>13.72476756847308</v>
+        <v>22.18452120682118</v>
       </c>
       <c r="I2">
-        <v>14.73322723846218</v>
+        <v>21.75163970266726</v>
       </c>
       <c r="J2">
-        <v>16.04992042884665</v>
+        <v>26.50284215128991</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2629,25 +2453,25 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.8384200000000001</v>
+        <v>0.83871</v>
       </c>
       <c r="C3">
-        <v>0.87608</v>
+        <v>0.87695</v>
       </c>
       <c r="D3">
-        <v>0.87408</v>
+        <v>0.87287</v>
       </c>
       <c r="E3">
-        <v>0.87698</v>
+        <v>0.87659</v>
       </c>
       <c r="H3">
-        <v>4.491782161685063</v>
+        <v>4.559382861775829</v>
       </c>
       <c r="I3">
-        <v>4.253238233820747</v>
+        <v>4.072921510414814</v>
       </c>
       <c r="J3">
-        <v>4.599126929224007</v>
+        <v>4.516459801361618</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2655,25 +2479,25 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0.74368</v>
+        <v>0.74134</v>
       </c>
       <c r="C4">
-        <v>0.8079</v>
+        <v>0.82117</v>
       </c>
       <c r="D4">
-        <v>0.82147</v>
+        <v>0.82345</v>
       </c>
       <c r="E4">
-        <v>0.8212</v>
+        <v>0.82152</v>
       </c>
       <c r="H4">
-        <v>8.635434595524949</v>
+        <v>10.76833841422289</v>
       </c>
       <c r="I4">
-        <v>10.46014414802066</v>
+        <v>11.07588960530931</v>
       </c>
       <c r="J4">
-        <v>10.42383820998279</v>
+        <v>10.81555021987213</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2681,25 +2505,25 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>0.41028</v>
+        <v>0.42139</v>
       </c>
       <c r="C5">
-        <v>0.46479</v>
+        <v>0.47398</v>
       </c>
       <c r="D5">
-        <v>0.60193</v>
+        <v>0.60687</v>
       </c>
       <c r="E5">
-        <v>0.59901</v>
+        <v>0.60553</v>
       </c>
       <c r="H5">
-        <v>13.28604855220825</v>
+        <v>12.4801252996037</v>
       </c>
       <c r="I5">
-        <v>46.71200155991031</v>
+        <v>44.01623199411473</v>
       </c>
       <c r="J5">
-        <v>46.00029248318224</v>
+        <v>43.6982367877738</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2707,25 +2531,25 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0.58324</v>
+        <v>0.57596</v>
       </c>
       <c r="C6">
-        <v>0.609</v>
+        <v>0.60729</v>
       </c>
       <c r="D6">
-        <v>0.61386</v>
+        <v>0.60826</v>
       </c>
       <c r="E6">
-        <v>0.60997</v>
+        <v>0.60528</v>
       </c>
       <c r="H6">
-        <v>4.416706673067692</v>
+        <v>5.439613862073749</v>
       </c>
       <c r="I6">
-        <v>5.249982854399557</v>
+        <v>5.608028335301062</v>
       </c>
       <c r="J6">
-        <v>4.583018997325292</v>
+        <v>5.090631293839852</v>
       </c>
     </row>
   </sheetData>
@@ -2787,37 +2611,37 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>0.37274</v>
+        <v>0.36925</v>
       </c>
       <c r="C2">
-        <v>0.40226</v>
+        <v>0.39533</v>
       </c>
       <c r="D2">
-        <v>0.40869</v>
+        <v>0.40007</v>
       </c>
       <c r="E2">
-        <v>0.40704</v>
+        <v>0.40222</v>
       </c>
       <c r="F2">
-        <v>0.61185</v>
+        <v>0.60908</v>
       </c>
       <c r="G2">
-        <v>0.62443</v>
+        <v>0.60975</v>
       </c>
       <c r="H2">
-        <v>7.919729570209795</v>
+        <v>7.062965470548406</v>
       </c>
       <c r="I2">
-        <v>9.644792616837469</v>
+        <v>8.346648612051444</v>
       </c>
       <c r="J2">
-        <v>9.202124805494446</v>
+        <v>8.928909952606634</v>
       </c>
       <c r="K2">
-        <v>64.14927295165531</v>
+        <v>64.95057549085983</v>
       </c>
       <c r="L2">
-        <v>67.52427965874337</v>
+        <v>65.13202437373053</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2825,37 +2649,37 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.94203</v>
+        <v>0.9402700000000001</v>
       </c>
       <c r="C3">
-        <v>0.96063</v>
+        <v>0.96545</v>
       </c>
       <c r="D3">
-        <v>0.95679</v>
+        <v>0.96543</v>
       </c>
       <c r="E3">
-        <v>0.95424</v>
+        <v>0.9638</v>
       </c>
       <c r="F3">
-        <v>1.1511</v>
+        <v>1.14668</v>
       </c>
       <c r="G3">
-        <v>1.15575</v>
+        <v>1.15959</v>
       </c>
       <c r="H3">
-        <v>1.974459412120628</v>
+        <v>2.677954204643345</v>
       </c>
       <c r="I3">
-        <v>1.566829081876373</v>
+        <v>2.675827156029646</v>
       </c>
       <c r="J3">
-        <v>1.296137065698539</v>
+        <v>2.502472694013415</v>
       </c>
       <c r="K3">
-        <v>22.19356071462692</v>
+        <v>21.95220521765023</v>
       </c>
       <c r="L3">
-        <v>22.68717556765708</v>
+        <v>23.32521509779104</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2863,37 +2687,37 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0.63866</v>
+        <v>0.63531</v>
       </c>
       <c r="C4">
-        <v>0.69172</v>
+        <v>0.70186</v>
       </c>
       <c r="D4">
-        <v>0.69535</v>
+        <v>0.69881</v>
       </c>
       <c r="E4">
-        <v>0.69321</v>
+        <v>0.69853</v>
       </c>
       <c r="F4">
-        <v>0.87485</v>
+        <v>0.86689</v>
       </c>
       <c r="G4">
-        <v>0.88347</v>
+        <v>0.8817199999999999</v>
       </c>
       <c r="H4">
-        <v>8.308019916700591</v>
+        <v>10.47520108293589</v>
       </c>
       <c r="I4">
-        <v>8.876397457175965</v>
+        <v>9.99512049235806</v>
       </c>
       <c r="J4">
-        <v>8.541320890614724</v>
+        <v>9.951047520108284</v>
       </c>
       <c r="K4">
-        <v>36.98211881126107</v>
+        <v>36.45149612000441</v>
       </c>
       <c r="L4">
-        <v>38.33181974759653</v>
+        <v>38.78578961451888</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2901,37 +2725,37 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>1.43401</v>
+        <v>1.45088</v>
       </c>
       <c r="C5">
-        <v>1.47491</v>
+        <v>1.48913</v>
       </c>
       <c r="D5">
-        <v>1.53855</v>
+        <v>1.55071</v>
       </c>
       <c r="E5">
-        <v>1.53651</v>
+        <v>1.55158</v>
       </c>
       <c r="F5">
-        <v>1.90899</v>
+        <v>1.90653</v>
       </c>
       <c r="G5">
-        <v>2.02937</v>
+        <v>2.0111</v>
       </c>
       <c r="H5">
-        <v>2.852141895802675</v>
+        <v>2.636331054256735</v>
       </c>
       <c r="I5">
-        <v>7.290046791863382</v>
+        <v>6.880651742390831</v>
       </c>
       <c r="J5">
-        <v>7.147788369676642</v>
+        <v>6.940615350683724</v>
       </c>
       <c r="K5">
-        <v>33.12250263247815</v>
+        <v>31.40507829730923</v>
       </c>
       <c r="L5">
-        <v>41.51714423190913</v>
+        <v>38.6124283193648</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2939,37 +2763,37 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0.6906</v>
+        <v>0.65083</v>
       </c>
       <c r="C6">
-        <v>0.65367</v>
+        <v>0.63658</v>
       </c>
       <c r="D6">
-        <v>0.65915</v>
+        <v>0.63914</v>
       </c>
       <c r="E6">
-        <v>0.6523600000000001</v>
+        <v>0.63974</v>
       </c>
       <c r="F6">
-        <v>0.84053</v>
+        <v>0.82348</v>
       </c>
       <c r="G6">
-        <v>0.84519</v>
+        <v>0.83275</v>
       </c>
       <c r="H6">
-        <v>-5.347523892267596</v>
+        <v>-2.189511854094</v>
       </c>
       <c r="I6">
-        <v>-4.554011004923252</v>
+        <v>-1.796167970130445</v>
       </c>
       <c r="J6">
-        <v>-5.537214016796979</v>
+        <v>-1.703977997326498</v>
       </c>
       <c r="K6">
-        <v>21.71010715320012</v>
+        <v>26.52766467433892</v>
       </c>
       <c r="L6">
-        <v>22.38488271068636</v>
+        <v>27.95199975416007</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2977,37 +2801,37 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>0.38645</v>
+        <v>0.38339</v>
       </c>
       <c r="C7">
-        <v>0.43977</v>
+        <v>0.43824</v>
       </c>
       <c r="D7">
-        <v>0.44166</v>
+        <v>0.44397</v>
       </c>
       <c r="E7">
-        <v>0.44779</v>
+        <v>0.44632</v>
       </c>
       <c r="F7">
-        <v>0.65926</v>
+        <v>0.6571</v>
       </c>
       <c r="G7">
-        <v>0.67709</v>
+        <v>0.6764</v>
       </c>
       <c r="H7">
-        <v>13.79738646655453</v>
+        <v>14.3065807663215</v>
       </c>
       <c r="I7">
-        <v>14.28645361625048</v>
+        <v>15.80114243981324</v>
       </c>
       <c r="J7">
-        <v>15.87268728166645</v>
+        <v>16.41409530765017</v>
       </c>
       <c r="K7">
-        <v>70.59386725320221</v>
+        <v>71.39205508750879</v>
       </c>
       <c r="L7">
-        <v>75.20765946435502</v>
+        <v>76.42609353399932</v>
       </c>
     </row>
   </sheetData>

--- a/finetrace_overhead_stat.xlsx
+++ b/finetrace_overhead_stat.xlsx
@@ -23,13 +23,13 @@
     <t>clean</t>
   </si>
   <si>
-    <t>host-timing</t>
-  </si>
-  <si>
     <t>call-logging</t>
   </si>
   <si>
-    <t>host+call</t>
+    <t>device-timeline</t>
+  </si>
+  <si>
+    <t>call+device</t>
   </si>
   <si>
     <t>metrics</t>
@@ -38,13 +38,13 @@
     <t>all</t>
   </si>
   <si>
-    <t>host-timing (%)</t>
-  </si>
-  <si>
     <t>call-logging (%)</t>
   </si>
   <si>
-    <t>host+call (%)</t>
+    <t>device-timeline (%)</t>
+  </si>
+  <si>
+    <t>call+device (%)</t>
   </si>
   <si>
     <t>metrics (%)</t>
@@ -189,19 +189,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.1435</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.83871</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.74134</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.42139</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.57596</c:v>
+                  <c:v>1.05127</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8414199999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.76411</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.44946</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.57281</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -211,7 +211,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>FineTrace: хост-тайминг (1)</c:v>
+            <c:v>FineTrace: трейсинг API-вызовов (1)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -253,19 +253,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.39718</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.87695</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.82117</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.47398</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.60729</c:v>
+                  <c:v>1.06304</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.85776</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.82657</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.56614</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.59742</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -275,7 +275,7 @@
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:v>FineTrace: трейсинг вызовов (2)</c:v>
+            <c:v>FineTrace: трейсинг GPU-событий (2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -317,19 +317,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.39223</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.87287</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.82345</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.60687</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.60826</c:v>
+                  <c:v>1.06371</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.86833</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8143899999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.51159</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.61348</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -381,19 +381,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.44656</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.87659</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.82152</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.60553</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.60528</c:v>
+                  <c:v>1.09622</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8712800000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.81846</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.61113</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5968</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -609,7 +609,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>FineTrace: хост-тайминг (1)</c:v>
+            <c:v>FineTrace: трейсинг API-вызовов (1)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -651,19 +651,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>22.18452120682118</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.559382861775829</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.76833841422289</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>12.4801252996037</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.439613862073749</c:v>
+                  <c:v>1.119598200272057</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.94195526609779</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.174215754276226</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25.96004093801449</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.29636354113928</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -673,7 +673,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>FineTrace: трейсинг вызовов (2)</c:v>
+            <c:v>FineTrace: трейсинг GPU-событий (2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -715,19 +715,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>21.75163970266726</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.072921510414814</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>11.07588960530931</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>44.01623199411473</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.608028335301062</c:v>
+                  <c:v>1.183330638180487</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.198165006774275</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.58020442082946</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13.82325457215324</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.100085543199312</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -779,19 +779,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>26.50284215128991</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.516459801361618</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.81555021987213</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>43.6982367877738</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.090631293839852</c:v>
+                  <c:v>4.275780722364383</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.548762805733178</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.112850244074807</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35.96983046322251</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.188125207311317</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1052,22 +1052,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.36925</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.9402700000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.63531</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.45088</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.65083</c:v>
+                  <c:v>0.38908</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.93506</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.65798</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.56415</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.60428</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.38339</c:v>
+                  <c:v>0.38038</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1077,7 +1077,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>FineTrace: хост-тайминг (1)</c:v>
+            <c:v>FineTrace: трейсинг API-вызовов (1)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1122,22 +1122,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.39533</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.96545</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.70186</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.48913</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.63658</c:v>
+                  <c:v>0.40374</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96956</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.70744</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.55453</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.6255500000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.43824</c:v>
+                  <c:v>0.42447</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1147,7 +1147,7 @@
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:v>FineTrace: трейсинг вызовов (2)</c:v>
+            <c:v>FineTrace: трейсинг GPU-событий (2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1192,22 +1192,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.40007</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.96543</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.69881</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.55071</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.63914</c:v>
+                  <c:v>0.4063</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96535</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.7194199999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.63397</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.64399</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.44397</c:v>
+                  <c:v>0.46418</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1262,22 +1262,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.40222</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.9638</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.69853</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.55158</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.63974</c:v>
+                  <c:v>0.42332</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96593</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6903899999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7238</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.63465</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.44632</c:v>
+                  <c:v>0.46421</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1332,22 +1332,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.60908</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.14668</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.86689</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.90653</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.82348</c:v>
+                  <c:v>0.59099</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.12813</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.89164</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.93509</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8294</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.6571</c:v>
+                  <c:v>0.64079</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1402,22 +1402,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.60975</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.15959</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.8817199999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.0111</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.83275</c:v>
+                  <c:v>0.6259</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.14617</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.86875</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.9846</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.81476</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.6764</c:v>
+                  <c:v>0.65059</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1535,7 +1535,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>FineTrace: хост-тайминг (1)</c:v>
+            <c:v>FineTrace: трейсинг API-вызовов (1)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1580,22 +1580,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.062965470548406</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.677954204643345</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.47520108293589</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.636331054256735</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-2.189511854094</c:v>
+                  <c:v>3.767862650354685</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.68960280623703</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.516945803823817</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.6150305277626802</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.519891441053818</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.3065807663215</c:v>
+                  <c:v>11.59104053840896</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1605,7 +1605,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>FineTrace: трейсинг вызовов (2)</c:v>
+            <c:v>FineTrace: трейсинг GPU-событий (2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1650,22 +1650,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>8.346648612051444</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.675827156029646</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.99512049235806</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.880651742390831</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-1.796167970130445</c:v>
+                  <c:v>4.425825023131493</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.239364318867243</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.337669837988988</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.463766262826455</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.571456940491148</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>15.80114243981324</c:v>
+                  <c:v>22.0306009779694</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1720,22 +1720,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>8.928909952606634</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.502472694013415</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.951047520108284</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.940615350683724</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-1.703977997326498</c:v>
+                  <c:v>8.80024673588979</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.301392424015566</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.925681631660527</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10.20682159639421</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.025815846958364</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>16.41409530765017</c:v>
+                  <c:v>22.03848782796152</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1790,22 +1790,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>64.95057549085983</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>21.95220521765023</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>36.45149612000441</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>31.40507829730923</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>26.52766467433892</c:v>
+                  <c:v>51.89421198725199</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.64787286377346</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35.51171768138849</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.71511683662053</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>37.25425299530018</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>71.39205508750879</c:v>
+                  <c:v>68.46048688153951</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1860,22 +1860,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>65.13202437373053</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>23.32521509779104</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>38.78578961451888</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>38.6124283193648</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>27.95199975416007</c:v>
+                  <c:v>60.86665981289197</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.57716082390434</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>32.03288853764552</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26.88041428251766</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>34.83153504997683</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>76.42609353399932</c:v>
+                  <c:v>71.03685787896315</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2427,25 +2427,25 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>1.1435</v>
+        <v>1.05127</v>
       </c>
       <c r="C2">
-        <v>1.39718</v>
+        <v>1.06304</v>
       </c>
       <c r="D2">
-        <v>1.39223</v>
+        <v>1.06371</v>
       </c>
       <c r="E2">
-        <v>1.44656</v>
+        <v>1.09622</v>
       </c>
       <c r="H2">
-        <v>22.18452120682118</v>
+        <v>1.119598200272057</v>
       </c>
       <c r="I2">
-        <v>21.75163970266726</v>
+        <v>1.183330638180487</v>
       </c>
       <c r="J2">
-        <v>26.50284215128991</v>
+        <v>4.275780722364383</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2453,25 +2453,25 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.83871</v>
+        <v>0.8414199999999999</v>
       </c>
       <c r="C3">
-        <v>0.87695</v>
+        <v>0.85776</v>
       </c>
       <c r="D3">
-        <v>0.87287</v>
+        <v>0.86833</v>
       </c>
       <c r="E3">
-        <v>0.87659</v>
+        <v>0.8712800000000001</v>
       </c>
       <c r="H3">
-        <v>4.559382861775829</v>
+        <v>1.94195526609779</v>
       </c>
       <c r="I3">
-        <v>4.072921510414814</v>
+        <v>3.198165006774275</v>
       </c>
       <c r="J3">
-        <v>4.516459801361618</v>
+        <v>3.548762805733178</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2479,25 +2479,25 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0.74134</v>
+        <v>0.76411</v>
       </c>
       <c r="C4">
-        <v>0.82117</v>
+        <v>0.82657</v>
       </c>
       <c r="D4">
-        <v>0.82345</v>
+        <v>0.8143899999999999</v>
       </c>
       <c r="E4">
-        <v>0.82152</v>
+        <v>0.81846</v>
       </c>
       <c r="H4">
-        <v>10.76833841422289</v>
+        <v>8.174215754276226</v>
       </c>
       <c r="I4">
-        <v>11.07588960530931</v>
+        <v>6.58020442082946</v>
       </c>
       <c r="J4">
-        <v>10.81555021987213</v>
+        <v>7.112850244074807</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2505,25 +2505,25 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>0.42139</v>
+        <v>0.44946</v>
       </c>
       <c r="C5">
-        <v>0.47398</v>
+        <v>0.56614</v>
       </c>
       <c r="D5">
-        <v>0.60687</v>
+        <v>0.51159</v>
       </c>
       <c r="E5">
-        <v>0.60553</v>
+        <v>0.61113</v>
       </c>
       <c r="H5">
-        <v>12.4801252996037</v>
+        <v>25.96004093801449</v>
       </c>
       <c r="I5">
-        <v>44.01623199411473</v>
+        <v>13.82325457215324</v>
       </c>
       <c r="J5">
-        <v>43.6982367877738</v>
+        <v>35.96983046322251</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2531,25 +2531,25 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0.57596</v>
+        <v>0.57281</v>
       </c>
       <c r="C6">
-        <v>0.60729</v>
+        <v>0.59742</v>
       </c>
       <c r="D6">
-        <v>0.60826</v>
+        <v>0.61348</v>
       </c>
       <c r="E6">
-        <v>0.60528</v>
+        <v>0.5968</v>
       </c>
       <c r="H6">
-        <v>5.439613862073749</v>
+        <v>4.29636354113928</v>
       </c>
       <c r="I6">
-        <v>5.608028335301062</v>
+        <v>7.100085543199312</v>
       </c>
       <c r="J6">
-        <v>5.090631293839852</v>
+        <v>4.188125207311317</v>
       </c>
     </row>
   </sheetData>
@@ -2611,37 +2611,37 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>0.36925</v>
+        <v>0.38908</v>
       </c>
       <c r="C2">
-        <v>0.39533</v>
+        <v>0.40374</v>
       </c>
       <c r="D2">
-        <v>0.40007</v>
+        <v>0.4063</v>
       </c>
       <c r="E2">
-        <v>0.40222</v>
+        <v>0.42332</v>
       </c>
       <c r="F2">
-        <v>0.60908</v>
+        <v>0.59099</v>
       </c>
       <c r="G2">
-        <v>0.60975</v>
+        <v>0.6259</v>
       </c>
       <c r="H2">
-        <v>7.062965470548406</v>
+        <v>3.767862650354685</v>
       </c>
       <c r="I2">
-        <v>8.346648612051444</v>
+        <v>4.425825023131493</v>
       </c>
       <c r="J2">
-        <v>8.928909952606634</v>
+        <v>8.80024673588979</v>
       </c>
       <c r="K2">
-        <v>64.95057549085983</v>
+        <v>51.89421198725199</v>
       </c>
       <c r="L2">
-        <v>65.13202437373053</v>
+        <v>60.86665981289197</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2649,37 +2649,37 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.9402700000000001</v>
+        <v>0.93506</v>
       </c>
       <c r="C3">
-        <v>0.96545</v>
+        <v>0.96956</v>
       </c>
       <c r="D3">
-        <v>0.96543</v>
+        <v>0.96535</v>
       </c>
       <c r="E3">
-        <v>0.9638</v>
+        <v>0.96593</v>
       </c>
       <c r="F3">
-        <v>1.14668</v>
+        <v>1.12813</v>
       </c>
       <c r="G3">
-        <v>1.15959</v>
+        <v>1.14617</v>
       </c>
       <c r="H3">
-        <v>2.677954204643345</v>
+        <v>3.68960280623703</v>
       </c>
       <c r="I3">
-        <v>2.675827156029646</v>
+        <v>3.239364318867243</v>
       </c>
       <c r="J3">
-        <v>2.502472694013415</v>
+        <v>3.301392424015566</v>
       </c>
       <c r="K3">
-        <v>21.95220521765023</v>
+        <v>20.64787286377346</v>
       </c>
       <c r="L3">
-        <v>23.32521509779104</v>
+        <v>22.57716082390434</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2687,37 +2687,37 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0.63531</v>
+        <v>0.65798</v>
       </c>
       <c r="C4">
-        <v>0.70186</v>
+        <v>0.70744</v>
       </c>
       <c r="D4">
-        <v>0.69881</v>
+        <v>0.7194199999999999</v>
       </c>
       <c r="E4">
-        <v>0.69853</v>
+        <v>0.6903899999999999</v>
       </c>
       <c r="F4">
-        <v>0.86689</v>
+        <v>0.89164</v>
       </c>
       <c r="G4">
-        <v>0.8817199999999999</v>
+        <v>0.86875</v>
       </c>
       <c r="H4">
-        <v>10.47520108293589</v>
+        <v>7.516945803823817</v>
       </c>
       <c r="I4">
-        <v>9.99512049235806</v>
+        <v>9.337669837988988</v>
       </c>
       <c r="J4">
-        <v>9.951047520108284</v>
+        <v>4.925681631660527</v>
       </c>
       <c r="K4">
-        <v>36.45149612000441</v>
+        <v>35.51171768138849</v>
       </c>
       <c r="L4">
-        <v>38.78578961451888</v>
+        <v>32.03288853764552</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2725,37 +2725,37 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>1.45088</v>
+        <v>1.56415</v>
       </c>
       <c r="C5">
-        <v>1.48913</v>
+        <v>1.55453</v>
       </c>
       <c r="D5">
-        <v>1.55071</v>
+        <v>1.63397</v>
       </c>
       <c r="E5">
-        <v>1.55158</v>
+        <v>1.7238</v>
       </c>
       <c r="F5">
-        <v>1.90653</v>
+        <v>1.93509</v>
       </c>
       <c r="G5">
-        <v>2.0111</v>
+        <v>1.9846</v>
       </c>
       <c r="H5">
-        <v>2.636331054256735</v>
+        <v>-0.6150305277626802</v>
       </c>
       <c r="I5">
-        <v>6.880651742390831</v>
+        <v>4.463766262826455</v>
       </c>
       <c r="J5">
-        <v>6.940615350683724</v>
+        <v>10.20682159639421</v>
       </c>
       <c r="K5">
-        <v>31.40507829730923</v>
+        <v>23.71511683662053</v>
       </c>
       <c r="L5">
-        <v>38.6124283193648</v>
+        <v>26.88041428251766</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2763,37 +2763,37 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0.65083</v>
+        <v>0.60428</v>
       </c>
       <c r="C6">
-        <v>0.63658</v>
+        <v>0.6255500000000001</v>
       </c>
       <c r="D6">
-        <v>0.63914</v>
+        <v>0.64399</v>
       </c>
       <c r="E6">
-        <v>0.63974</v>
+        <v>0.63465</v>
       </c>
       <c r="F6">
-        <v>0.82348</v>
+        <v>0.8294</v>
       </c>
       <c r="G6">
-        <v>0.83275</v>
+        <v>0.81476</v>
       </c>
       <c r="H6">
-        <v>-2.189511854094</v>
+        <v>3.519891441053818</v>
       </c>
       <c r="I6">
-        <v>-1.796167970130445</v>
+        <v>6.571456940491148</v>
       </c>
       <c r="J6">
-        <v>-1.703977997326498</v>
+        <v>5.025815846958364</v>
       </c>
       <c r="K6">
-        <v>26.52766467433892</v>
+        <v>37.25425299530018</v>
       </c>
       <c r="L6">
-        <v>27.95199975416007</v>
+        <v>34.83153504997683</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2801,37 +2801,37 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>0.38339</v>
+        <v>0.38038</v>
       </c>
       <c r="C7">
-        <v>0.43824</v>
+        <v>0.42447</v>
       </c>
       <c r="D7">
-        <v>0.44397</v>
+        <v>0.46418</v>
       </c>
       <c r="E7">
-        <v>0.44632</v>
+        <v>0.46421</v>
       </c>
       <c r="F7">
-        <v>0.6571</v>
+        <v>0.64079</v>
       </c>
       <c r="G7">
-        <v>0.6764</v>
+        <v>0.65059</v>
       </c>
       <c r="H7">
-        <v>14.3065807663215</v>
+        <v>11.59104053840896</v>
       </c>
       <c r="I7">
-        <v>15.80114243981324</v>
+        <v>22.0306009779694</v>
       </c>
       <c r="J7">
-        <v>16.41409530765017</v>
+        <v>22.03848782796152</v>
       </c>
       <c r="K7">
-        <v>71.39205508750879</v>
+        <v>68.46048688153951</v>
       </c>
       <c r="L7">
-        <v>76.42609353399932</v>
+        <v>71.03685787896315</v>
       </c>
     </row>
   </sheetData>

--- a/finetrace_overhead_stat.xlsx
+++ b/finetrace_overhead_stat.xlsx
@@ -189,19 +189,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.05127</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.8414199999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.76411</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.44946</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.57281</c:v>
+                  <c:v>1.00984</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.83611</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.73538</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.40992</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5886</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -253,19 +253,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.06304</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.85776</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.82657</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.56614</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.59742</c:v>
+                  <c:v>1.03413</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.86572</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.81446</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.52771</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.61759</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -317,19 +317,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.06371</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.86833</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.8143899999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.51159</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.61348</c:v>
+                  <c:v>1.25614</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.87021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.80643</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.47711</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.60798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -381,19 +381,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.09622</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.8712800000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.81846</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.61113</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.5968</c:v>
+                  <c:v>1.31824</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.86109</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.80704</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.54039</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.61371</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -651,19 +651,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.119598200272057</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.94195526609779</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.174215754276226</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>25.96004093801449</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.29636354113928</c:v>
+                  <c:v>2.405331537669326</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.541400055016687</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.75362397671951</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>28.73487509758002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.925246347264689</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -715,19 +715,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.183330638180487</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.198165006774275</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6.58020442082946</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>13.82325457215324</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.100085543199312</c:v>
+                  <c:v>24.39000237661411</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.078410735429551</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.661671516766834</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.39100312256049</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.292558613659523</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -779,19 +779,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>4.275780722364383</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.548762805733178</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.112850244074807</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>35.96983046322251</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.188125207311317</c:v>
+                  <c:v>30.53949140457895</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.987645166305869</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.744621828170462</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31.82816159250586</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.266055045871553</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1052,22 +1052,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.38908</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.93506</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.65798</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.56415</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.60428</c:v>
+                  <c:v>0.37348</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.93493</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.633</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.44707</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.63711</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.38038</c:v>
+                  <c:v>0.39344</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1122,22 +1122,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.40374</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.96956</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.70744</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.55453</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.6255500000000001</c:v>
+                  <c:v>0.41379</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96932</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.698</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.54603</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.66315</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.42447</c:v>
+                  <c:v>0.45072</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1192,22 +1192,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.4063</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.96535</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.7194199999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.63397</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.64399</c:v>
+                  <c:v>0.42724</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96798</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.7031500000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.66267</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.67827</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.46418</c:v>
+                  <c:v>0.47242</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1262,22 +1262,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.42332</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.96593</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.6903899999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.7238</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.63465</c:v>
+                  <c:v>0.42337</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96928</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69813</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.70867</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.71003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.46421</c:v>
+                  <c:v>0.48814</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1332,22 +1332,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.59099</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.12813</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.89164</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.93509</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.8294</c:v>
+                  <c:v>0.61253</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.14581</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.87476</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.91594</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.84261</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.64079</c:v>
+                  <c:v>0.66836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1402,22 +1402,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.6259</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.14617</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.86875</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.9846</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.81476</c:v>
+                  <c:v>0.62362</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1563</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.87851</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.06493</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.82877</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.65059</c:v>
+                  <c:v>0.67505</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1580,22 +1580,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.767862650354685</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.68960280623703</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.516945803823817</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.6150305277626802</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.519891441053818</c:v>
+                  <c:v>10.79308128949342</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.678350250820908</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.26856240126381</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.838646368178453</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.087206290907389</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.59104053840896</c:v>
+                  <c:v>14.5587637250915</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1650,22 +1650,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.425825023131493</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.239364318867243</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.337669837988988</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.463766262826455</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6.571456940491148</c:v>
+                  <c:v>14.39434507871908</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.535024012492904</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.08214849921012</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.89907191773722</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.460422846918129</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>22.0306009779694</c:v>
+                  <c:v>20.07421716144774</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1720,22 +1720,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>8.80024673588979</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.301392424015566</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.925681631660527</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10.20682159639421</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.025815846958364</c:v>
+                  <c:v>13.35814501445862</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.674071855646946</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.28909952606636</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.07790915436018</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.44543328467613</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>22.03848782796152</c:v>
+                  <c:v>24.06974379829199</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1790,22 +1790,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>51.89421198725199</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>20.64787286377346</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>35.51171768138849</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>23.71511683662053</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>37.25425299530018</c:v>
+                  <c:v>64.00610474456465</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.55569935717112</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38.19273301737756</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>32.40133511163938</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32.255026604511</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>68.46048688153951</c:v>
+                  <c:v>69.87596583977225</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1860,22 +1860,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>60.86665981289197</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>22.57716082390434</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>32.03288853764552</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>26.88041428251766</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>34.83153504997683</c:v>
+                  <c:v>66.97547392095962</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23.67770849154483</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38.78515007898894</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>42.69731250043189</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.08271727017314</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>71.03685787896315</c:v>
+                  <c:v>71.57635217568118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2427,25 +2427,25 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>1.05127</v>
+        <v>1.00984</v>
       </c>
       <c r="C2">
-        <v>1.06304</v>
+        <v>1.03413</v>
       </c>
       <c r="D2">
-        <v>1.06371</v>
+        <v>1.25614</v>
       </c>
       <c r="E2">
-        <v>1.09622</v>
+        <v>1.31824</v>
       </c>
       <c r="H2">
-        <v>1.119598200272057</v>
+        <v>2.405331537669326</v>
       </c>
       <c r="I2">
-        <v>1.183330638180487</v>
+        <v>24.39000237661411</v>
       </c>
       <c r="J2">
-        <v>4.275780722364383</v>
+        <v>30.53949140457895</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2453,25 +2453,25 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.8414199999999999</v>
+        <v>0.83611</v>
       </c>
       <c r="C3">
-        <v>0.85776</v>
+        <v>0.86572</v>
       </c>
       <c r="D3">
-        <v>0.86833</v>
+        <v>0.87021</v>
       </c>
       <c r="E3">
-        <v>0.8712800000000001</v>
+        <v>0.86109</v>
       </c>
       <c r="H3">
-        <v>1.94195526609779</v>
+        <v>3.541400055016687</v>
       </c>
       <c r="I3">
-        <v>3.198165006774275</v>
+        <v>4.078410735429551</v>
       </c>
       <c r="J3">
-        <v>3.548762805733178</v>
+        <v>2.987645166305869</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2479,25 +2479,25 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0.76411</v>
+        <v>0.73538</v>
       </c>
       <c r="C4">
-        <v>0.82657</v>
+        <v>0.81446</v>
       </c>
       <c r="D4">
-        <v>0.8143899999999999</v>
+        <v>0.80643</v>
       </c>
       <c r="E4">
-        <v>0.81846</v>
+        <v>0.80704</v>
       </c>
       <c r="H4">
-        <v>8.174215754276226</v>
+        <v>10.75362397671951</v>
       </c>
       <c r="I4">
-        <v>6.58020442082946</v>
+        <v>9.661671516766834</v>
       </c>
       <c r="J4">
-        <v>7.112850244074807</v>
+        <v>9.744621828170462</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2505,25 +2505,25 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>0.44946</v>
+        <v>0.40992</v>
       </c>
       <c r="C5">
-        <v>0.56614</v>
+        <v>0.52771</v>
       </c>
       <c r="D5">
-        <v>0.51159</v>
+        <v>0.47711</v>
       </c>
       <c r="E5">
-        <v>0.61113</v>
+        <v>0.54039</v>
       </c>
       <c r="H5">
-        <v>25.96004093801449</v>
+        <v>28.73487509758002</v>
       </c>
       <c r="I5">
-        <v>13.82325457215324</v>
+        <v>16.39100312256049</v>
       </c>
       <c r="J5">
-        <v>35.96983046322251</v>
+        <v>31.82816159250586</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2531,25 +2531,25 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0.57281</v>
+        <v>0.5886</v>
       </c>
       <c r="C6">
-        <v>0.59742</v>
+        <v>0.61759</v>
       </c>
       <c r="D6">
-        <v>0.61348</v>
+        <v>0.60798</v>
       </c>
       <c r="E6">
-        <v>0.5968</v>
+        <v>0.61371</v>
       </c>
       <c r="H6">
-        <v>4.29636354113928</v>
+        <v>4.925246347264689</v>
       </c>
       <c r="I6">
-        <v>7.100085543199312</v>
+        <v>3.292558613659523</v>
       </c>
       <c r="J6">
-        <v>4.188125207311317</v>
+        <v>4.266055045871553</v>
       </c>
     </row>
   </sheetData>
@@ -2611,37 +2611,37 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>0.38908</v>
+        <v>0.37348</v>
       </c>
       <c r="C2">
-        <v>0.40374</v>
+        <v>0.41379</v>
       </c>
       <c r="D2">
-        <v>0.4063</v>
+        <v>0.42724</v>
       </c>
       <c r="E2">
-        <v>0.42332</v>
+        <v>0.42337</v>
       </c>
       <c r="F2">
-        <v>0.59099</v>
+        <v>0.61253</v>
       </c>
       <c r="G2">
-        <v>0.6259</v>
+        <v>0.62362</v>
       </c>
       <c r="H2">
-        <v>3.767862650354685</v>
+        <v>10.79308128949342</v>
       </c>
       <c r="I2">
-        <v>4.425825023131493</v>
+        <v>14.39434507871908</v>
       </c>
       <c r="J2">
-        <v>8.80024673588979</v>
+        <v>13.35814501445862</v>
       </c>
       <c r="K2">
-        <v>51.89421198725199</v>
+        <v>64.00610474456465</v>
       </c>
       <c r="L2">
-        <v>60.86665981289197</v>
+        <v>66.97547392095962</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2649,37 +2649,37 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.93506</v>
+        <v>0.93493</v>
       </c>
       <c r="C3">
-        <v>0.96956</v>
+        <v>0.96932</v>
       </c>
       <c r="D3">
-        <v>0.96535</v>
+        <v>0.96798</v>
       </c>
       <c r="E3">
-        <v>0.96593</v>
+        <v>0.96928</v>
       </c>
       <c r="F3">
-        <v>1.12813</v>
+        <v>1.14581</v>
       </c>
       <c r="G3">
-        <v>1.14617</v>
+        <v>1.1563</v>
       </c>
       <c r="H3">
-        <v>3.68960280623703</v>
+        <v>3.678350250820908</v>
       </c>
       <c r="I3">
-        <v>3.239364318867243</v>
+        <v>3.535024012492904</v>
       </c>
       <c r="J3">
-        <v>3.301392424015566</v>
+        <v>3.674071855646946</v>
       </c>
       <c r="K3">
-        <v>20.64787286377346</v>
+        <v>22.55569935717112</v>
       </c>
       <c r="L3">
-        <v>22.57716082390434</v>
+        <v>23.67770849154483</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2687,37 +2687,37 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0.65798</v>
+        <v>0.633</v>
       </c>
       <c r="C4">
-        <v>0.70744</v>
+        <v>0.698</v>
       </c>
       <c r="D4">
-        <v>0.7194199999999999</v>
+        <v>0.7031500000000001</v>
       </c>
       <c r="E4">
-        <v>0.6903899999999999</v>
+        <v>0.69813</v>
       </c>
       <c r="F4">
-        <v>0.89164</v>
+        <v>0.87476</v>
       </c>
       <c r="G4">
-        <v>0.86875</v>
+        <v>0.87851</v>
       </c>
       <c r="H4">
-        <v>7.516945803823817</v>
+        <v>10.26856240126381</v>
       </c>
       <c r="I4">
-        <v>9.337669837988988</v>
+        <v>11.08214849921012</v>
       </c>
       <c r="J4">
-        <v>4.925681631660527</v>
+        <v>10.28909952606636</v>
       </c>
       <c r="K4">
-        <v>35.51171768138849</v>
+        <v>38.19273301737756</v>
       </c>
       <c r="L4">
-        <v>32.03288853764552</v>
+        <v>38.78515007898894</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2725,37 +2725,37 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>1.56415</v>
+        <v>1.44707</v>
       </c>
       <c r="C5">
-        <v>1.55453</v>
+        <v>1.54603</v>
       </c>
       <c r="D5">
-        <v>1.63397</v>
+        <v>1.66267</v>
       </c>
       <c r="E5">
-        <v>1.7238</v>
+        <v>1.70867</v>
       </c>
       <c r="F5">
-        <v>1.93509</v>
+        <v>1.91594</v>
       </c>
       <c r="G5">
-        <v>1.9846</v>
+        <v>2.06493</v>
       </c>
       <c r="H5">
-        <v>-0.6150305277626802</v>
+        <v>6.838646368178453</v>
       </c>
       <c r="I5">
-        <v>4.463766262826455</v>
+        <v>14.89907191773722</v>
       </c>
       <c r="J5">
-        <v>10.20682159639421</v>
+        <v>18.07790915436018</v>
       </c>
       <c r="K5">
-        <v>23.71511683662053</v>
+        <v>32.40133511163938</v>
       </c>
       <c r="L5">
-        <v>26.88041428251766</v>
+        <v>42.69731250043189</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2763,37 +2763,37 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0.60428</v>
+        <v>0.63711</v>
       </c>
       <c r="C6">
-        <v>0.6255500000000001</v>
+        <v>0.66315</v>
       </c>
       <c r="D6">
-        <v>0.64399</v>
+        <v>0.67827</v>
       </c>
       <c r="E6">
-        <v>0.63465</v>
+        <v>0.71003</v>
       </c>
       <c r="F6">
-        <v>0.8294</v>
+        <v>0.84261</v>
       </c>
       <c r="G6">
-        <v>0.81476</v>
+        <v>0.82877</v>
       </c>
       <c r="H6">
-        <v>3.519891441053818</v>
+        <v>4.087206290907389</v>
       </c>
       <c r="I6">
-        <v>6.571456940491148</v>
+        <v>6.460422846918129</v>
       </c>
       <c r="J6">
-        <v>5.025815846958364</v>
+        <v>11.44543328467613</v>
       </c>
       <c r="K6">
-        <v>37.25425299530018</v>
+        <v>32.255026604511</v>
       </c>
       <c r="L6">
-        <v>34.83153504997683</v>
+        <v>30.08271727017314</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2801,37 +2801,37 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>0.38038</v>
+        <v>0.39344</v>
       </c>
       <c r="C7">
-        <v>0.42447</v>
+        <v>0.45072</v>
       </c>
       <c r="D7">
-        <v>0.46418</v>
+        <v>0.47242</v>
       </c>
       <c r="E7">
-        <v>0.46421</v>
+        <v>0.48814</v>
       </c>
       <c r="F7">
-        <v>0.64079</v>
+        <v>0.66836</v>
       </c>
       <c r="G7">
-        <v>0.65059</v>
+        <v>0.67505</v>
       </c>
       <c r="H7">
-        <v>11.59104053840896</v>
+        <v>14.5587637250915</v>
       </c>
       <c r="I7">
-        <v>22.0306009779694</v>
+        <v>20.07421716144774</v>
       </c>
       <c r="J7">
-        <v>22.03848782796152</v>
+        <v>24.06974379829199</v>
       </c>
       <c r="K7">
-        <v>68.46048688153951</v>
+        <v>69.87596583977225</v>
       </c>
       <c r="L7">
-        <v>71.03685787896315</v>
+        <v>71.57635217568118</v>
       </c>
     </row>
   </sheetData>

--- a/finetrace_overhead_stat.xlsx
+++ b/finetrace_overhead_stat.xlsx
@@ -189,19 +189,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.00984</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.83611</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.73538</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.40992</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.5886</c:v>
+                  <c:v>1.02004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.84311</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.74416</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.41125</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.58506</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -211,7 +211,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>FineTrace: трейсинг API-вызовов (1)</c:v>
+            <c:v>FineTrace: отслеживание API-вызовов (1)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -253,19 +253,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.03413</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.86572</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.81446</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.52771</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.61759</c:v>
+                  <c:v>1.05411</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8783300000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.80217</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.5208</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.62216</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -275,7 +275,7 @@
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:v>FineTrace: трейсинг GPU-событий (2)</c:v>
+            <c:v>FineTrace: отслеживание GPU-событий (2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -317,19 +317,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.25614</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.87021</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.80643</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.47711</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.60798</c:v>
+                  <c:v>1.33039</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.87627</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.81532</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.46704</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.61122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -381,19 +381,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.31824</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.86109</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.80704</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.54039</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.61371</c:v>
+                  <c:v>1.41995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.88262</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.81475</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.54643</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.62077</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -403,7 +403,7 @@
           <c:idx val="4"/>
           <c:order val="4"/>
           <c:tx>
-            <c:v>FineTrace: метрики GPU (3)</c:v>
+            <c:v>FineTrace: сбор GPU-метрик (3)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -609,7 +609,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>FineTrace: трейсинг API-вызовов (1)</c:v>
+            <c:v>FineTrace: отслеживание API-вызовов (1)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -651,19 +651,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2.405331537669326</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.541400055016687</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.75362397671951</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>28.73487509758002</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.925246347264689</c:v>
+                  <c:v>3.340065095486456</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.177390850541451</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.795366587830574</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26.63829787234043</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.341229959320414</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -673,7 +673,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>FineTrace: трейсинг GPU-событий (2)</c:v>
+            <c:v>FineTrace: отслеживание GPU-событий (2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -715,19 +715,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>24.39000237661411</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.078410735429551</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.661671516766834</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>16.39100312256049</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.292558613659523</c:v>
+                  <c:v>30.42527744010038</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.933057370924312</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.562459686089014</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13.56595744680851</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.471336273202741</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -779,19 +779,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>30.53949140457895</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.987645166305869</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.744621828170462</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>31.82816159250586</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.266055045871553</c:v>
+                  <c:v>39.20532528136151</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.686221252268379</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.485863255213921</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>32.87051671732522</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.103647489146415</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -801,7 +801,7 @@
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
-            <c:v>FineTrace: метрики GPU (3)</c:v>
+            <c:v>FineTrace: сбор GPU-метрик (3)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1052,22 +1052,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.37348</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.93493</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.633</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.44707</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.63711</c:v>
+                  <c:v>0.38352</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.65522</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.45514</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.62846</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.39344</c:v>
+                  <c:v>0.43035</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1077,7 +1077,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>FineTrace: трейсинг API-вызовов (1)</c:v>
+            <c:v>FineTrace: отслеживание API-вызовов (1)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1122,22 +1122,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.41379</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.96932</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.698</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.54603</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.66315</c:v>
+                  <c:v>0.41683</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98431</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.70481</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.54665</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.66162</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.45072</c:v>
+                  <c:v>0.4706</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1147,7 +1147,7 @@
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:v>FineTrace: трейсинг GPU-событий (2)</c:v>
+            <c:v>FineTrace: отслеживание GPU-событий (2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1192,22 +1192,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.42724</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.96798</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.7031500000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.66267</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.67827</c:v>
+                  <c:v>0.44029</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99094</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.71367</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.71067</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.67214</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.47242</c:v>
+                  <c:v>0.50671</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1262,22 +1262,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.42337</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.96928</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.69813</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.70867</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.71003</c:v>
+                  <c:v>0.44757</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97892</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.7025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.70571</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.6864400000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.48814</c:v>
+                  <c:v>0.51456</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1287,7 +1287,7 @@
           <c:idx val="4"/>
           <c:order val="4"/>
           <c:tx>
-            <c:v>FineTrace: метрики GPU (3)</c:v>
+            <c:v>FineTrace: сбор GPU-метрик (3)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1332,22 +1332,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.61253</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.14581</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.87476</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.91594</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.84261</c:v>
+                  <c:v>0.59753</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1537</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.88434</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.9321</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.83123</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.66836</c:v>
+                  <c:v>0.69331</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1402,22 +1402,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.62362</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.1563</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.87851</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.06493</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.82877</c:v>
+                  <c:v>0.65539</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.15755</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8712</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.97913</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.84374</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.67505</c:v>
+                  <c:v>0.69489</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1535,7 +1535,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>FineTrace: трейсинг API-вызовов (1)</c:v>
+            <c:v>FineTrace: отслеживание API-вызовов (1)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1580,22 +1580,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10.79308128949342</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.678350250820908</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.26856240126381</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.838646368178453</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.087206290907389</c:v>
+                  <c:v>8.685335836462231</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.525883798929233</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.568450291505147</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.288741976717015</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.276389905483239</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.5587637250915</c:v>
+                  <c:v>9.352852329499246</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1605,7 +1605,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>FineTrace: трейсинг GPU-событий (2)</c:v>
+            <c:v>FineTrace: отслеживание GPU-событий (2)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1650,22 +1650,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>14.39434507871908</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.535024012492904</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>11.08214849921012</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>14.89907191773722</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6.460422846918129</c:v>
+                  <c:v>14.80235711305798</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.216465637564321</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.920667867281217</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17.56050964168395</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.950323011806629</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20.07421716144774</c:v>
+                  <c:v>17.74369699082142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1720,22 +1720,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>13.35814501445862</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.674071855646946</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.28909952606636</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>18.07790915436018</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>11.44543328467613</c:v>
+                  <c:v>16.700563204005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.964460554548673</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.215896950642531</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17.21964896848413</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.225726378767151</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24.06974379829199</c:v>
+                  <c:v>19.56779365632624</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1745,7 +1745,7 @@
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
-            <c:v>FineTrace: метрики GPU (3)</c:v>
+            <c:v>FineTrace: сбор GPU-метрик (3)</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1790,22 +1790,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>64.00610474456465</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>22.55569935717112</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>38.19273301737756</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>32.40133511163938</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>32.255026604511</c:v>
+                  <c:v>55.80152273675426</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.16957273503738</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>34.96840755776686</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>32.77760215511908</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32.2645832670337</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>69.87596583977225</c:v>
+                  <c:v>61.10375275938189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1860,22 +1860,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>66.97547392095962</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>23.67770849154483</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>38.78515007898894</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>42.69731250043189</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>30.08271727017314</c:v>
+                  <c:v>70.88808927826449</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.57058933816637</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>32.96297426818472</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>36.00959357862473</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>34.25516341533272</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>71.57635217568118</c:v>
+                  <c:v>61.47089578250261</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2427,25 +2427,25 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>1.00984</v>
+        <v>1.02004</v>
       </c>
       <c r="C2">
-        <v>1.03413</v>
+        <v>1.05411</v>
       </c>
       <c r="D2">
-        <v>1.25614</v>
+        <v>1.33039</v>
       </c>
       <c r="E2">
-        <v>1.31824</v>
+        <v>1.41995</v>
       </c>
       <c r="H2">
-        <v>2.405331537669326</v>
+        <v>3.340065095486456</v>
       </c>
       <c r="I2">
-        <v>24.39000237661411</v>
+        <v>30.42527744010038</v>
       </c>
       <c r="J2">
-        <v>30.53949140457895</v>
+        <v>39.20532528136151</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2453,25 +2453,25 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.83611</v>
+        <v>0.84311</v>
       </c>
       <c r="C3">
-        <v>0.86572</v>
+        <v>0.8783300000000001</v>
       </c>
       <c r="D3">
-        <v>0.87021</v>
+        <v>0.87627</v>
       </c>
       <c r="E3">
-        <v>0.86109</v>
+        <v>0.88262</v>
       </c>
       <c r="H3">
-        <v>3.541400055016687</v>
+        <v>4.177390850541451</v>
       </c>
       <c r="I3">
-        <v>4.078410735429551</v>
+        <v>3.933057370924312</v>
       </c>
       <c r="J3">
-        <v>2.987645166305869</v>
+        <v>4.686221252268379</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2479,25 +2479,25 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0.73538</v>
+        <v>0.74416</v>
       </c>
       <c r="C4">
-        <v>0.81446</v>
+        <v>0.80217</v>
       </c>
       <c r="D4">
-        <v>0.80643</v>
+        <v>0.81532</v>
       </c>
       <c r="E4">
-        <v>0.80704</v>
+        <v>0.81475</v>
       </c>
       <c r="H4">
-        <v>10.75362397671951</v>
+        <v>7.795366587830574</v>
       </c>
       <c r="I4">
-        <v>9.661671516766834</v>
+        <v>9.562459686089014</v>
       </c>
       <c r="J4">
-        <v>9.744621828170462</v>
+        <v>9.485863255213921</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2505,25 +2505,25 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>0.40992</v>
+        <v>0.41125</v>
       </c>
       <c r="C5">
-        <v>0.52771</v>
+        <v>0.5208</v>
       </c>
       <c r="D5">
-        <v>0.47711</v>
+        <v>0.46704</v>
       </c>
       <c r="E5">
-        <v>0.54039</v>
+        <v>0.54643</v>
       </c>
       <c r="H5">
-        <v>28.73487509758002</v>
+        <v>26.63829787234043</v>
       </c>
       <c r="I5">
-        <v>16.39100312256049</v>
+        <v>13.56595744680851</v>
       </c>
       <c r="J5">
-        <v>31.82816159250586</v>
+        <v>32.87051671732522</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2531,25 +2531,25 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0.5886</v>
+        <v>0.58506</v>
       </c>
       <c r="C6">
-        <v>0.61759</v>
+        <v>0.62216</v>
       </c>
       <c r="D6">
-        <v>0.60798</v>
+        <v>0.61122</v>
       </c>
       <c r="E6">
-        <v>0.61371</v>
+        <v>0.62077</v>
       </c>
       <c r="H6">
-        <v>4.925246347264689</v>
+        <v>6.341229959320414</v>
       </c>
       <c r="I6">
-        <v>3.292558613659523</v>
+        <v>4.471336273202741</v>
       </c>
       <c r="J6">
-        <v>4.266055045871553</v>
+        <v>6.103647489146415</v>
       </c>
     </row>
   </sheetData>
@@ -2611,37 +2611,37 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>0.37348</v>
+        <v>0.38352</v>
       </c>
       <c r="C2">
-        <v>0.41379</v>
+        <v>0.41683</v>
       </c>
       <c r="D2">
-        <v>0.42724</v>
+        <v>0.44029</v>
       </c>
       <c r="E2">
-        <v>0.42337</v>
+        <v>0.44757</v>
       </c>
       <c r="F2">
-        <v>0.61253</v>
+        <v>0.59753</v>
       </c>
       <c r="G2">
-        <v>0.62362</v>
+        <v>0.65539</v>
       </c>
       <c r="H2">
-        <v>10.79308128949342</v>
+        <v>8.685335836462231</v>
       </c>
       <c r="I2">
-        <v>14.39434507871908</v>
+        <v>14.80235711305798</v>
       </c>
       <c r="J2">
-        <v>13.35814501445862</v>
+        <v>16.700563204005</v>
       </c>
       <c r="K2">
-        <v>64.00610474456465</v>
+        <v>55.80152273675426</v>
       </c>
       <c r="L2">
-        <v>66.97547392095962</v>
+        <v>70.88808927826449</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2649,37 +2649,37 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.93493</v>
+        <v>0.96006</v>
       </c>
       <c r="C3">
-        <v>0.96932</v>
+        <v>0.98431</v>
       </c>
       <c r="D3">
-        <v>0.96798</v>
+        <v>0.99094</v>
       </c>
       <c r="E3">
-        <v>0.96928</v>
+        <v>0.97892</v>
       </c>
       <c r="F3">
-        <v>1.14581</v>
+        <v>1.1537</v>
       </c>
       <c r="G3">
-        <v>1.1563</v>
+        <v>1.15755</v>
       </c>
       <c r="H3">
-        <v>3.678350250820908</v>
+        <v>2.525883798929233</v>
       </c>
       <c r="I3">
-        <v>3.535024012492904</v>
+        <v>3.216465637564321</v>
       </c>
       <c r="J3">
-        <v>3.674071855646946</v>
+        <v>1.964460554548673</v>
       </c>
       <c r="K3">
-        <v>22.55569935717112</v>
+        <v>20.16957273503738</v>
       </c>
       <c r="L3">
-        <v>23.67770849154483</v>
+        <v>20.57058933816637</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2687,37 +2687,37 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0.633</v>
+        <v>0.65522</v>
       </c>
       <c r="C4">
-        <v>0.698</v>
+        <v>0.70481</v>
       </c>
       <c r="D4">
-        <v>0.7031500000000001</v>
+        <v>0.71367</v>
       </c>
       <c r="E4">
-        <v>0.69813</v>
+        <v>0.7025</v>
       </c>
       <c r="F4">
-        <v>0.87476</v>
+        <v>0.88434</v>
       </c>
       <c r="G4">
-        <v>0.87851</v>
+        <v>0.8712</v>
       </c>
       <c r="H4">
-        <v>10.26856240126381</v>
+        <v>7.568450291505147</v>
       </c>
       <c r="I4">
-        <v>11.08214849921012</v>
+        <v>8.920667867281217</v>
       </c>
       <c r="J4">
-        <v>10.28909952606636</v>
+        <v>7.215896950642531</v>
       </c>
       <c r="K4">
-        <v>38.19273301737756</v>
+        <v>34.96840755776686</v>
       </c>
       <c r="L4">
-        <v>38.78515007898894</v>
+        <v>32.96297426818472</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2725,37 +2725,37 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>1.44707</v>
+        <v>1.45514</v>
       </c>
       <c r="C5">
-        <v>1.54603</v>
+        <v>1.54665</v>
       </c>
       <c r="D5">
-        <v>1.66267</v>
+        <v>1.71067</v>
       </c>
       <c r="E5">
-        <v>1.70867</v>
+        <v>1.70571</v>
       </c>
       <c r="F5">
-        <v>1.91594</v>
+        <v>1.9321</v>
       </c>
       <c r="G5">
-        <v>2.06493</v>
+        <v>1.97913</v>
       </c>
       <c r="H5">
-        <v>6.838646368178453</v>
+        <v>6.288741976717015</v>
       </c>
       <c r="I5">
-        <v>14.89907191773722</v>
+        <v>17.56050964168395</v>
       </c>
       <c r="J5">
-        <v>18.07790915436018</v>
+        <v>17.21964896848413</v>
       </c>
       <c r="K5">
-        <v>32.40133511163938</v>
+        <v>32.77760215511908</v>
       </c>
       <c r="L5">
-        <v>42.69731250043189</v>
+        <v>36.00959357862473</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2763,37 +2763,37 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0.63711</v>
+        <v>0.62846</v>
       </c>
       <c r="C6">
-        <v>0.66315</v>
+        <v>0.66162</v>
       </c>
       <c r="D6">
-        <v>0.67827</v>
+        <v>0.67214</v>
       </c>
       <c r="E6">
-        <v>0.71003</v>
+        <v>0.6864400000000001</v>
       </c>
       <c r="F6">
-        <v>0.84261</v>
+        <v>0.83123</v>
       </c>
       <c r="G6">
-        <v>0.82877</v>
+        <v>0.84374</v>
       </c>
       <c r="H6">
-        <v>4.087206290907389</v>
+        <v>5.276389905483239</v>
       </c>
       <c r="I6">
-        <v>6.460422846918129</v>
+        <v>6.950323011806629</v>
       </c>
       <c r="J6">
-        <v>11.44543328467613</v>
+        <v>9.225726378767151</v>
       </c>
       <c r="K6">
-        <v>32.255026604511</v>
+        <v>32.2645832670337</v>
       </c>
       <c r="L6">
-        <v>30.08271727017314</v>
+        <v>34.25516341533272</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2801,37 +2801,37 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>0.39344</v>
+        <v>0.43035</v>
       </c>
       <c r="C7">
-        <v>0.45072</v>
+        <v>0.4706</v>
       </c>
       <c r="D7">
-        <v>0.47242</v>
+        <v>0.50671</v>
       </c>
       <c r="E7">
-        <v>0.48814</v>
+        <v>0.51456</v>
       </c>
       <c r="F7">
-        <v>0.66836</v>
+        <v>0.69331</v>
       </c>
       <c r="G7">
-        <v>0.67505</v>
+        <v>0.69489</v>
       </c>
       <c r="H7">
-        <v>14.5587637250915</v>
+        <v>9.352852329499246</v>
       </c>
       <c r="I7">
-        <v>20.07421716144774</v>
+        <v>17.74369699082142</v>
       </c>
       <c r="J7">
-        <v>24.06974379829199</v>
+        <v>19.56779365632624</v>
       </c>
       <c r="K7">
-        <v>69.87596583977225</v>
+        <v>61.10375275938189</v>
       </c>
       <c r="L7">
-        <v>71.57635217568118</v>
+        <v>61.47089578250261</v>
       </c>
     </row>
   </sheetData>
